--- a/MediaRightsOverview.xlsx
+++ b/MediaRightsOverview.xlsx
@@ -8,14 +8,19 @@
     <sheet name="Method" sheetId="4" r:id="rId4"/>
     <sheet name="Reconciliation" sheetId="5" r:id="rId5"/>
     <sheet name="Media_Rights_Calendar" sheetId="6" r:id="rId6"/>
+    <sheet name="2026 vs 2025" sheetId="7" r:id="rId7"/>
+    <sheet name="2027 vs 2026" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="+#,##0;-#,##0"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -51,10 +56,10 @@
   </fills>
   <borders count="9">
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -73,11 +78,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -92,30 +119,17 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -128,20 +142,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="756">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -277,6 +282,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -412,6 +444,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -547,6 +606,33 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -682,6 +768,33 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -817,6 +930,33 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -952,6 +1092,33 @@
     <xf numFmtId="4" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1087,6 +1254,33 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1221,6 +1415,1005 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1237,60 +2430,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Field</t>
         </is>
       </c>
-      <c r="B1" s="139" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="93" t="inlineStr">
+      <c r="B2" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Media Rights Overview</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Media Rights.xlsx plus verified primary announcements</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Anchor</t>
         </is>
       </c>
-      <c r="B4" s="93" t="inlineStr">
+      <c r="B4" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K media rights revenue $1,212.25m</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Currency</t>
         </is>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">USD millions</t>
         </is>
@@ -1302,7 +2495,7 @@
           <t xml:space="preserve">Created</t>
         </is>
       </c>
-      <c r="B6" s="95" t="inlineStr">
+      <c r="B6" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-28</t>
         </is>
@@ -1327,54 +2520,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal</t>
         </is>
       </c>
-      <c r="B1" s="53" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Term</t>
         </is>
       </c>
-      <c r="D1" s="53" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start</t>
         </is>
       </c>
-      <c r="E1" s="53" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Term End</t>
         </is>
       </c>
-      <c r="F1" s="53" t="inlineStr">
+      <c r="F1" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="G1" s="233" t="inlineStr">
+      <c r="G1" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">2028 Revenue (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="323" t="inlineStr">
+      <c r="H1" s="385" t="inlineStr">
         <is>
           <t xml:space="preserve">Share of 2028 Total</t>
         </is>
       </c>
-      <c r="I1" s="49" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">In 2028 Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (pooled residual) — F2/F3, archive, radio, ancillary</t>
         </is>
@@ -1402,20 +2595,20 @@
           <t xml:space="preserve">ASSUMP</t>
         </is>
       </c>
-      <c r="G2" s="186">
+      <c r="G2" s="222">
         <v>388.2</v>
       </c>
-      <c r="H2" s="276">
+      <c r="H2" s="330">
         <v>0.25555445837859186</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -1443,20 +2636,20 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G3" s="186">
+      <c r="G3" s="222">
         <v>181.8</v>
       </c>
-      <c r="H3" s="276">
+      <c r="H3" s="330">
         <v>0.11968006319739312</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -1482,20 +2675,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G4" s="186">
+      <c r="G4" s="222">
         <v>145</v>
       </c>
-      <c r="H4" s="276">
+      <c r="H4" s="330">
         <v>0.09545439583950496</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -1521,20 +2714,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G5" s="186">
+      <c r="G5" s="222">
         <v>127.85</v>
       </c>
-      <c r="H5" s="276">
+      <c r="H5" s="330">
         <v>0.08416444488331523</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -1560,20 +2753,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G6" s="186">
+      <c r="G6" s="222">
         <v>71.7</v>
       </c>
-      <c r="H6" s="276">
+      <c r="H6" s="330">
         <v>0.0472005529771897</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -1599,20 +2792,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G7" s="186">
+      <c r="G7" s="222">
         <v>69.68</v>
       </c>
-      <c r="H7" s="276">
+      <c r="H7" s="330">
         <v>0.045870774497218665</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -1638,20 +2831,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G8" s="186">
+      <c r="G8" s="222">
         <v>61.87</v>
       </c>
-      <c r="H8" s="276">
+      <c r="H8" s="330">
         <v>0.04072940324544946</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -1677,20 +2870,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G9" s="186">
+      <c r="G9" s="222">
         <v>50.96</v>
       </c>
-      <c r="H9" s="276">
+      <c r="H9" s="330">
         <v>0.033547282841249464</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -1716,20 +2909,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G10" s="186">
+      <c r="G10" s="222">
         <v>49.03</v>
       </c>
-      <c r="H10" s="276">
+      <c r="H10" s="330">
         <v>0.03227675191731674</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Kayo Sports / Foxtel</t>
         </is>
@@ -1755,20 +2948,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G11" s="186">
+      <c r="G11" s="222">
         <v>43.68</v>
       </c>
-      <c r="H11" s="276">
+      <c r="H11" s="330">
         <v>0.028754813863928114</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -1794,20 +2987,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G12" s="186">
+      <c r="G12" s="222">
         <v>37.86</v>
       </c>
-      <c r="H12" s="276">
+      <c r="H12" s="330">
         <v>0.024923471906783845</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -1833,20 +3026,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G13" s="186">
+      <c r="G13" s="222">
         <v>32.7</v>
       </c>
-      <c r="H13" s="276">
+      <c r="H13" s="330">
         <v>0.021526612027253877</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -1872,20 +3065,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G14" s="186">
+      <c r="G14" s="222">
         <v>32.45</v>
       </c>
-      <c r="H14" s="276">
+      <c r="H14" s="330">
         <v>0.021362035482703007</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -1911,20 +3104,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G15" s="186">
+      <c r="G15" s="222">
         <v>25</v>
       </c>
-      <c r="H15" s="276">
+      <c r="H15" s="330">
         <v>0.01645765445508706</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -1950,20 +3143,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G16" s="186">
+      <c r="G16" s="222">
         <v>22.9</v>
       </c>
-      <c r="H16" s="276">
+      <c r="H16" s="330">
         <v>0.015075211480859748</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -1989,20 +3182,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G17" s="186">
+      <c r="G17" s="222">
         <v>20.4</v>
       </c>
-      <c r="H17" s="276">
+      <c r="H17" s="330">
         <v>0.013429446035351041</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -2028,20 +3221,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G18" s="186">
+      <c r="G18" s="222">
         <v>18.72</v>
       </c>
-      <c r="H18" s="276">
+      <c r="H18" s="330">
         <v>0.012323491655969191</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — other digital</t>
         </is>
@@ -2069,20 +3262,20 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G19" s="186">
+      <c r="G19" s="222">
         <v>18.6</v>
       </c>
-      <c r="H19" s="276">
+      <c r="H19" s="330">
         <v>0.012244494914584774</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -2108,20 +3301,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G20" s="186">
+      <c r="G20" s="222">
         <v>18.03</v>
       </c>
-      <c r="H20" s="276">
+      <c r="H20" s="330">
         <v>0.01186926039300879</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -2147,20 +3340,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G21" s="186">
+      <c r="G21" s="222">
         <v>15.38</v>
       </c>
-      <c r="H21" s="276">
+      <c r="H21" s="330">
         <v>0.01012474902076956</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -2188,20 +3381,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G22" s="186">
+      <c r="G22" s="222">
         <v>11.9</v>
       </c>
-      <c r="H22" s="276">
+      <c r="H22" s="330">
         <v>0.007833843520621442</v>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -2229,20 +3422,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G23" s="186">
+      <c r="G23" s="222">
         <v>10.82</v>
       </c>
-      <c r="H23" s="276">
+      <c r="H23" s="330">
         <v>0.00712287284816168</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -2268,20 +3461,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G24" s="186">
+      <c r="G24" s="222">
         <v>9.86</v>
       </c>
-      <c r="H24" s="276">
+      <c r="H24" s="330">
         <v>0.006490898917086337</v>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -2309,20 +3502,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G25" s="186">
+      <c r="G25" s="222">
         <v>8.65</v>
       </c>
-      <c r="H25" s="276">
+      <c r="H25" s="330">
         <v>0.005694348441460124</v>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -2348,20 +3541,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G26" s="186">
+      <c r="G26" s="222">
         <v>8.48</v>
       </c>
-      <c r="H26" s="276">
+      <c r="H26" s="330">
         <v>0.005582436391165532</v>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -2387,20 +3580,20 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G27" s="186">
+      <c r="G27" s="222">
         <v>8.32</v>
       </c>
-      <c r="H27" s="276">
+      <c r="H27" s="330">
         <v>0.0054771074026529745</v>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -2426,20 +3619,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G28" s="186">
+      <c r="G28" s="222">
         <v>6.49</v>
       </c>
-      <c r="H28" s="276">
+      <c r="H28" s="330">
         <v>0.004272407096540602</v>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -2465,20 +3658,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G29" s="186">
+      <c r="G29" s="222">
         <v>5.62</v>
       </c>
-      <c r="H29" s="276">
+      <c r="H29" s="330">
         <v>0.0036996807215035716</v>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -2504,20 +3697,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G30" s="186">
+      <c r="G30" s="222">
         <v>5.41</v>
       </c>
-      <c r="H30" s="276">
+      <c r="H30" s="330">
         <v>0.00356143642408084</v>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -2543,20 +3736,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G31" s="186">
+      <c r="G31" s="222">
         <v>4.87</v>
       </c>
-      <c r="H31" s="276">
+      <c r="H31" s="330">
         <v>0.0032059510878509594</v>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -2582,20 +3775,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G32" s="186">
+      <c r="G32" s="222">
         <v>3.12</v>
       </c>
-      <c r="H32" s="276">
+      <c r="H32" s="330">
         <v>0.0020539152759948653</v>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -2621,20 +3814,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G33" s="186">
+      <c r="G33" s="222">
         <v>2.08</v>
       </c>
-      <c r="H33" s="276">
+      <c r="H33" s="330">
         <v>0.0013692768506632436</v>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -2662,20 +3855,20 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G34" s="186">
+      <c r="G34" s="222">
         <v>1.62</v>
       </c>
-      <c r="H34" s="276">
+      <c r="H34" s="330">
         <v>0.0010664560086896416</v>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL</t>
         </is>
@@ -2701,13 +3894,13 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G35" s="186">
+      <c r="G35" s="222">
         <v>0</v>
       </c>
-      <c r="H35" s="276"/>
+      <c r="H35" s="330"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ORF</t>
         </is>
@@ -2733,13 +3926,13 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G36" s="186">
+      <c r="G36" s="222">
         <v>0</v>
       </c>
-      <c r="H36" s="276"/>
+      <c r="H36" s="330"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Band</t>
         </is>
@@ -2765,13 +3958,13 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G37" s="186">
+      <c r="G37" s="222">
         <v>0</v>
       </c>
-      <c r="H37" s="276"/>
+      <c r="H37" s="330"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 movie (Brad Pitt)</t>
         </is>
@@ -2797,10 +3990,10 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G38" s="186">
+      <c r="G38" s="222">
         <v>0</v>
       </c>
-      <c r="H38" s="276"/>
+      <c r="H38" s="330"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -2808,31 +4001,31 @@
           <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-2025</t>
         </is>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="8">
         <v>2023</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="8">
         <v>2025</v>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="224">
         <v>0</v>
       </c>
-      <c r="H39" s="277"/>
+      <c r="H39" s="332"/>
     </row>
   </sheetData>
 </worksheet>
@@ -2848,29 +4041,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Holder</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="62" t="inlineStr">
+      <c r="C1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">URLs Inspected</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">Named Citations (no public URL)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -2886,14 +4079,14 @@
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7 (Formula One Digital Media Ltd, subscription-based services $181.797m).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -2908,14 +4101,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 management commentary on the Liberty Media Q2 2026 earnings call (ex-US F1 TV revenue +18% YTD); base from FY2025 10-K Note 7.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — other digital</t>
         </is>
@@ -2930,14 +4123,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7, other digital media rights $18.589m.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -2952,14 +4145,14 @@
           <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple Newsroom, 17 Oct 2025 (no fee). Fee band: CNBC; Sports Business Journal/Puck; BBC ($750m over five years).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -2975,14 +4168,14 @@
 https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Sky, 6 May 2026 (term, no fee). Fee: SportsPro, £645m over seven years, cross-checked against the BlackBook F1 Business Report.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -2998,14 +4191,14 @@
 https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport Bild; GPBlog; WEB.DE, €50-55m a year. Multi-bidder 2028 tender: F1 management comments to Motorsport-Magazin, July 2026; DigitalFernsehen.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL</t>
         </is>
@@ -3020,14 +4213,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">DWDL, RTL and Sky sublicence arrangement.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -3042,14 +4235,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF ~€15m rights + ~€5m production for half-calendar sublicence; derStandard industry estimate &gt;€15m a year.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">ORF</t>
         </is>
@@ -3064,14 +4257,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF rights and production cost for the half-calendar sublicence.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -3086,14 +4279,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR service announcements; F1 broadcaster directory. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -3108,14 +4301,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Équipe, April 2022: &gt;€60m a year for France plus Francophone Africa.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -3130,14 +4323,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Équipe and RMC, Canal+ (Maxime Saada) on a significant increase. No figure published.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -3152,14 +4345,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and DAZN, 8 Sep 2026 (term). Fee: 2Playbook, Spain €40-50m; prior Telefónica face ~€45m.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -3174,14 +4367,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, NL plus Nordics package ~$47m a year; NOS, Telegraaf and TotaalTV on the Dutch €45m component.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -3196,14 +4389,14 @@
           <t xml:space="preserve">https://grupapolsatplus.pl/en/archive/formula-1-back-eleven-sports-network-has-secured-exclusive-rights-next-four-seasons</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Cyfrowy Polsat, 30 Oct 2024: exclusive 2025-28, record fee, no figure. Prior cycle ~$15m per GlobalData/Sportcal.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -3218,14 +4411,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Magyar Hang, prior package $43.39m over 2023-25; MTI, December 2025 renewal through 2027.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -3240,14 +4433,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nova Sport launch announcements; F1 broadcaster directory. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -3262,14 +4455,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Infront, Balkans sublicence June 2025; F1 broadcaster directory for the constituent territories. All fees unpublished.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -3284,14 +4477,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and ESPN, February 2026 (term, no fee). Prior cycle: SportsBusiness Journal on Mediapro, 2014.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -3306,14 +4499,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Globo, 11 Jul 2025 (term, no fee); fee ~$8m a year reported by UOL.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Band</t>
         </is>
@@ -3328,14 +4521,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Folha de S.Paulo, Band ~$15m a year.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -3350,14 +4543,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports Mexico exit, ~$1.5m for six races; Televisa/Sky Mexico renewal reported late 2025, fee undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -3372,14 +4565,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-and-bell-medias-tsn-and-rds-announce-multi-year-media-rights-extension-for-canada/</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Bell Media, 2 Mar 2020: multi-year extension (term only, no fee). Canadian GP hosting agreement to 2035 reported by SportsBusiness Journal.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -3394,14 +4587,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Bloomberg and Reuters, November 2023: &gt;$500m over ten years.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -3416,14 +4609,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and beIN, February 2026 (term, no fee); Liberty Media Q1 2026 commentary on the pan-Asia extension.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -3438,14 +4631,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">SportBusiness, 2020: SuperSport fee steady. MultiChoice annual report, no F1 isolate.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -3460,14 +4653,14 @@
           <t xml:space="preserve">https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Fuji TV, 4 Dec 2025 (term, no fee); Sponichi, tens-of-billions-of-yen scale.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -3482,14 +4675,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Tencent renewal, term through 2027 (no fee); Lanxiong Sports on historic Chinese right values.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -3504,14 +4697,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and FanCode, December 2025 (term, no fee); SportBusiness on digital-only market value.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -3526,14 +4719,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play extension, September 2025; ELTA Chinese Taipei through 2029. Fees unpublished.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -3548,14 +4741,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sydney Morning Herald, A$45m a year for the incumbents.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Kayo Sports / Foxtel</t>
         </is>
@@ -3570,14 +4763,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1, Kayo and Foxtel new deal announced 2026; Sydney Morning Herald, A$60m a year from 2027.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -3592,14 +4785,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky New Zealand, September 2025 three-year renewal (no fee); Coliseum history ~$1.5m a year.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -3614,14 +4807,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">VOV, TV360 exclusive 2026-28. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -3636,14 +4829,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 broadcaster directory, in-ship and in-flight listing. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (pooled residual) — F2/F3, archive, radio, ancillary</t>
         </is>
@@ -3658,14 +4851,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A and Revenue Recognition note: media rights fees from F1 Event broadcast, F2 and F3 races, F1 TV subscriptions, origination and archive footage, radio and other ancillary media rights.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 movie (Brad Pitt)</t>
         </is>
@@ -3680,7 +4873,7 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A: one-time revenue associated with the release of the F1 movie.</t>
         </is>
@@ -3692,17 +4885,17 @@
           <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Sports Business Journal, June 2023: ESPN ~$87.5m a year.</t>
         </is>
@@ -3720,108 +4913,108 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Item</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis convention</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HARD = disclosed in a filing or by a party. TRADE = figure reported in trade or business press, parties silent. EST = modelled where no figure is published. ASSUMP = reconciliation residual.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Reported anchor</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K reports Formula 1 media rights revenue of $1,212.25m. That is the only total anchor; 2026-28 have no reported comparator.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Residual construction</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Pooled residual = $1,212.25m minus every other included row for 2025, held flat in dollars thereafter. Not escalated, so forward growth comes only from named deals.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Term column</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start and Term End hold four-digit years only. 'OPEN' means the term end has not been announced or is open-ended. Both columns are stored as text so a year is never reformatted.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">US step-up</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple at $131.5m in 2026 against ESPN at $87.5m in 2025 is a $44m, ~50% increase, the largest single-deal uplift in the book.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Term corrections vs source file</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky UK and Ireland now run to 2034 and Sky Italia to 2032 (both announced 6 May 2026). Apple and Globo both start in 2026, not 2025. Band ended with 2025.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Platform data</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Platform descriptions reflect the announced package per territory where a primary announcement was reviewed; otherwise the source file's package_type.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Excluded rows</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL, ORF and Network 10 are sublicences or free-to-air windows paid to the primary rights holder, not to F1; including them would double count. ESPN (to 2025), Band (to 2025) and the F1 movie are one-off or expired and sit outside the forward run rate.</t>
         </is>
@@ -3833,7 +5026,7 @@
           <t xml:space="preserve">Known weak points</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada media (bundled with GP hosting), Japan, Korea/SEA basket and Switzerland carry the widest ranges. Apple is the largest single forecast risk.</t>
         </is>
@@ -3854,26 +5047,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="63" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">Line</t>
         </is>
       </c>
-      <c r="B1" s="53">
+      <c r="B1" s="61">
         <v>2025</v>
       </c>
-      <c r="C1" s="53">
+      <c r="C1" s="61">
         <v>2026</v>
       </c>
-      <c r="D1" s="53">
+      <c r="D1" s="61">
         <v>2027</v>
       </c>
-      <c r="E1" s="49">
+      <c r="E1" s="54">
         <v>2028</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Named territory, DTC and designated-territory deals</t>
         </is>
@@ -3887,12 +5080,12 @@
       <c r="D2" s="6">
         <v>1032.59</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="5">
         <v>1066.03</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Pooled residual (F2/F3, archive, radio, ancillary)</t>
         </is>
@@ -3906,12 +5099,12 @@
       <c r="D3" s="6">
         <v>421.85</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>421.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Total modelled media revenue</t>
         </is>
@@ -3925,12 +5118,12 @@
       <c r="D4" s="6">
         <v>1454.44</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>1487.88</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty reported FY2025 media rights revenue</t>
         </is>
@@ -3944,7 +5137,7 @@
       <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3954,16 +5147,16 @@
           <t xml:space="preserve">Variance vs reported</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3991,79 +5184,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Media Rights Holder</t>
         </is>
       </c>
-      <c r="C1" s="62" t="inlineStr">
+      <c r="C1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Platforms / Broadcast Rights</t>
         </is>
       </c>
-      <c r="D1" s="80" t="inlineStr">
+      <c r="D1" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start</t>
         </is>
       </c>
-      <c r="E1" s="80" t="inlineStr">
+      <c r="E1" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Term End</t>
         </is>
       </c>
-      <c r="F1" s="80" t="inlineStr">
+      <c r="F1" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="G1" s="269" t="inlineStr">
+      <c r="G1" s="313" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2025 (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="269" t="inlineStr">
+      <c r="H1" s="313" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2026 (USD m)</t>
         </is>
       </c>
-      <c r="I1" s="269" t="inlineStr">
+      <c r="I1" s="313" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2027 (USD m)</t>
         </is>
       </c>
-      <c r="J1" s="269" t="inlineStr">
+      <c r="J1" s="313" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2028 (USD m)</t>
         </is>
       </c>
-      <c r="K1" s="80" t="inlineStr">
+      <c r="K1" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">In Total</t>
         </is>
       </c>
-      <c r="L1" s="62" t="inlineStr">
+      <c r="L1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
-      <c r="M1" s="62" t="inlineStr">
+      <c r="M1" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyst Notes</t>
         </is>
       </c>
-      <c r="N1" s="58" t="inlineStr">
+      <c r="N1" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">Sources</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Global ex-US</t>
         </is>
@@ -4091,16 +5284,16 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G2" s="222">
+      <c r="G2" s="258">
         <v>181.8</v>
       </c>
-      <c r="H2" s="222">
+      <c r="H2" s="258">
         <v>181.8</v>
       </c>
-      <c r="I2" s="222">
+      <c r="I2" s="258">
         <v>181.8</v>
       </c>
-      <c r="J2" s="222">
+      <c r="J2" s="258">
         <v>181.8</v>
       </c>
       <c r="K2" s="33" t="inlineStr">
@@ -4118,7 +5311,7 @@
           <t xml:space="preserve">The only audited, partner-level line in the stack: Liberty's FY2025 10-K puts subscription-based services at $181.797m. Source workbook carries a separate DTC_GROWTH row (+$32.7m, +18% ex-US YTD per the Q2 2026 call); it is a disclosed overlay on this same fee, so merging it prevents a double count. The FY2025 base is held flat and the 18% is treated as upside, because the US leaves this line in 2026.</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7 (Formula One Digital Media Ltd, subscription-based services $181.797m). Growth: Liberty Media Q2 2026 earnings call, ex-US F1 TV revenue +18% YTD.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm
@@ -4127,7 +5320,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -4155,16 +5348,16 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G3" s="222">
+      <c r="G3" s="258">
         <v>18.6</v>
       </c>
-      <c r="H3" s="222">
+      <c r="H3" s="258">
         <v>18.6</v>
       </c>
-      <c r="I3" s="222">
+      <c r="I3" s="258">
         <v>18.6</v>
       </c>
-      <c r="J3" s="222">
+      <c r="J3" s="258">
         <v>18.6</v>
       </c>
       <c r="K3" s="33" t="inlineStr">
@@ -4182,7 +5375,7 @@
           <t xml:space="preserve">Second disclosed line from the FY2025 10-K ($18.589m), event-contracted. Held flat for lack of growth disclosure; at under 2% of the total the flat carry is immaterial.</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7, other digital media rights $18.589m.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -4190,7 +5383,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
@@ -4216,16 +5409,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G4" s="222">
+      <c r="G4" s="258">
         <v>0</v>
       </c>
-      <c r="H4" s="222">
+      <c r="H4" s="258">
         <v>131.52</v>
       </c>
-      <c r="I4" s="222">
+      <c r="I4" s="258">
         <v>138.1</v>
       </c>
-      <c r="J4" s="222">
+      <c r="J4" s="258">
         <v>145</v>
       </c>
       <c r="K4" s="33" t="inlineStr">
@@ -4243,7 +5436,7 @@
           <t xml:space="preserve">$145m is the midpoint of the $140m (CNBC, SBJ/Puck) to $150m (BBC) trade band, reached on a 5% step from a $131.5m 2026 start so the package totals roughly $750m. Largest single forecast risk in the book: a $10m error moves the total by about 1%. Against ESPN's $87.5m the US fee rises roughly 50%.</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple Newsroom, 17 Oct 2025 (term, no fee). Fee band: CNBC; Sports Business Journal/Puck; BBC ($750m over five years).
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
@@ -4251,7 +5444,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
         </is>
@@ -4277,16 +5470,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G5" s="222">
+      <c r="G5" s="258">
         <v>0</v>
       </c>
-      <c r="H5" s="222">
+      <c r="H5" s="258">
         <v>35</v>
       </c>
-      <c r="I5" s="222">
+      <c r="I5" s="258">
         <v>36.4</v>
       </c>
-      <c r="J5" s="222">
+      <c r="J5" s="258">
         <v>37.86</v>
       </c>
       <c r="K5" s="33" t="inlineStr">
@@ -4304,7 +5497,7 @@
           <t xml:space="preserve">The one disclosed prior cycle (Mediapro, 2015-19) ran at about EUR20m+ a year, a floor well below the $35m carried here; the premium reflects DTS-era regional repricing. No trade print exists for the 2026-28 cycle, so the number is directional.</t>
         </is>
       </c>
-      <c r="N5" s="12" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and ESPN, February 2026 (term, no fee). Prior cycle: Sports Business Journal on Mediapro, 2014.
 https://corp.formula1.com/</t>
@@ -4312,7 +5505,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Brazil</t>
         </is>
@@ -4338,16 +5531,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G6" s="222">
+      <c r="G6" s="258">
         <v>0</v>
       </c>
-      <c r="H6" s="222">
+      <c r="H6" s="258">
         <v>7.69</v>
       </c>
-      <c r="I6" s="222">
+      <c r="I6" s="258">
         <v>8</v>
       </c>
-      <c r="J6" s="222">
+      <c r="J6" s="258">
         <v>8.32</v>
       </c>
       <c r="K6" s="33" t="inlineStr">
@@ -4365,7 +5558,7 @@
           <t xml:space="preserve">About $8m a year, below the $15m Band paid and below the $13m Record reportedly bid; Globo traded fee for reach. Brazil is the one large market where the renewal went down rather than up. The source workbook escalates from a $7.69m 2026 start, so the $8m trade figure lands in 2027.</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Globo, 11 Jul 2025 (term, no fee); fee ~$8m a year reported by UOL.
 https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
@@ -4373,7 +5566,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mexico</t>
         </is>
@@ -4399,16 +5592,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G7" s="222">
+      <c r="G7" s="258">
         <v>0</v>
       </c>
-      <c r="H7" s="222">
+      <c r="H7" s="258">
         <v>7.84</v>
       </c>
-      <c r="I7" s="222">
+      <c r="I7" s="258">
         <v>8.16</v>
       </c>
-      <c r="J7" s="222">
+      <c r="J7" s="258">
         <v>8.48</v>
       </c>
       <c r="K7" s="33" t="inlineStr">
@@ -4426,7 +5619,7 @@
           <t xml:space="preserve">Fox Sports paid about $1.5m for the last six races of 2025, a distressed exit that annualises to roughly $6m and sets a floor; Televisa repriced upward late in 2025. $8m sits above that floor. No published fee for the Televisa cycle.</t>
         </is>
       </c>
-      <c r="N7" s="12" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports Mexico exit, ~$1.5m for six races; Televisa/Sky Mexico renewal reported late 2025, fee undisclosed.
 https://corp.formula1.com/</t>
@@ -4434,7 +5627,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada</t>
         </is>
@@ -4460,16 +5653,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G8" s="222">
+      <c r="G8" s="258">
         <v>8.77</v>
       </c>
-      <c r="H8" s="222">
+      <c r="H8" s="258">
         <v>9.12</v>
       </c>
-      <c r="I8" s="222">
+      <c r="I8" s="258">
         <v>9.48</v>
       </c>
-      <c r="J8" s="222">
+      <c r="J8" s="258">
         <v>9.86</v>
       </c>
       <c r="K8" s="33" t="inlineStr">
@@ -4487,7 +5680,7 @@
           <t xml:space="preserve">Rights are bundled with Canadian GP hosting and neither Bell nor F1 disclosed a media fee. The estimate is an $8-10m cable package escalated to about $12m by end of term. Boundary that matters: the separate ~$18.7m GP hosting fee sits on the race-promotion calendar and must not be added here.</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Bell Media, 2 Mar 2020: multi-year extension (term only, no fee). Canadian GP hosting agreement to 2035 reported by Sports Business Journal.
 https://corp.formula1.com/formula-1-and-bell-medias-tsn-and-rds-announce-multi-year-media-rights-extension-for-canada/</t>
@@ -4495,7 +5688,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">United Kingdom, Ireland &amp; Italy</t>
         </is>
@@ -4521,16 +5714,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G9" s="222">
+      <c r="G9" s="258">
         <v>113.59</v>
       </c>
-      <c r="H9" s="222">
+      <c r="H9" s="258">
         <v>117</v>
       </c>
-      <c r="I9" s="222">
+      <c r="I9" s="258">
         <v>120.51</v>
       </c>
-      <c r="J9" s="222">
+      <c r="J9" s="258">
         <v>124.13</v>
       </c>
       <c r="K9" s="33" t="inlineStr">
@@ -4548,7 +5741,7 @@
           <t xml:space="preserve">Neither party disclosed a fee; GBP645m over seven years (SportsPro/BlackBook) gives about $117m for the combined three-territory package at the 2025 level, escalated 3%. Two source rows are merged here: the 2023-29 package and the 2030-34 forward at $255m, which is not bookable because the current cycle still governs through 2029.</t>
         </is>
       </c>
-      <c r="N9" s="12" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Sky, 6 May 2026 (term, no fee). Fee: SportsPro, GBP645m over seven years, cross-checked against the BlackBook F1 Business Report.
 https://corp.formula1.com/formula-1-and-sky-agree-long-term-partnership-across-uk-ireland-and-italy/
@@ -4557,7 +5750,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Germany</t>
         </is>
@@ -4583,16 +5776,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G10" s="222">
+      <c r="G10" s="258">
         <v>55</v>
       </c>
-      <c r="H10" s="222">
+      <c r="H10" s="258">
         <v>57.2</v>
       </c>
-      <c r="I10" s="222">
+      <c r="I10" s="258">
         <v>59.49</v>
       </c>
-      <c r="J10" s="222">
+      <c r="J10" s="258">
         <v>61.87</v>
       </c>
       <c r="K10" s="33" t="inlineStr">
@@ -4610,7 +5803,7 @@
           <t xml:space="preserve">EUR50-55m band reported by Sport Bild, GPBlog and WEB.DE, taken at $55m and escalated 4%. Germany is the most likely territory for a step change under new RTL ownership. That upside stays in this note rather than in the numbers, because booking a tender placeholder would put $75m into 2028 the parties have not agreed.</t>
         </is>
       </c>
-      <c r="N10" s="12" t="inlineStr">
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport Bild; GPBlog; WEB.DE, EUR50-55m a year. 2028 tender: F1 management to Motorsport-Magazin, July 2026; DigitalFernsehen. RTL sublicence: DWDL.
 https://corp.formula1.com/</t>
@@ -4618,7 +5811,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Austria</t>
         </is>
@@ -4644,16 +5837,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G11" s="222">
+      <c r="G11" s="258">
         <v>16.64</v>
       </c>
-      <c r="H11" s="222">
+      <c r="H11" s="258">
         <v>17.31</v>
       </c>
-      <c r="I11" s="222">
+      <c r="I11" s="258">
         <v>18</v>
       </c>
-      <c r="J11" s="222">
+      <c r="J11" s="258">
         <v>18.72</v>
       </c>
       <c r="K11" s="33" t="inlineStr">
@@ -4671,7 +5864,7 @@
           <t xml:space="preserve">F1 has not published the fee. $18m is anchored off the disclosed ORF sublicence: oe24 reported ORF paying about EUR15m in rights plus EUR5m production for a half-calendar package, which sets a floor for the master deal ServusTV buys. derStandard's industry estimate above EUR15m a year corroborates. The ORF row in the source file is a reallocation of the same money, not an addition.</t>
         </is>
       </c>
-      <c r="N11" s="12" t="inlineStr">
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF ~EUR15m rights + ~EUR5m production for half-calendar sublicence; derStandard industry estimate &gt;EUR15m a year.
 https://corp.formula1.com/</t>
@@ -4679,7 +5872,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Switzerland</t>
         </is>
@@ -4707,16 +5900,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G12" s="222">
+      <c r="G12" s="258">
         <v>7.69</v>
       </c>
-      <c r="H12" s="222">
+      <c r="H12" s="258">
         <v>8</v>
       </c>
-      <c r="I12" s="222">
+      <c r="I12" s="258">
         <v>8.32</v>
       </c>
-      <c r="J12" s="222">
+      <c r="J12" s="258">
         <v>8.65</v>
       </c>
       <c r="K12" s="33" t="inlineStr">
@@ -4734,7 +5927,7 @@
           <t xml:space="preserve">No disclosed figure in any Swiss public filing reviewed. $8m is a population-based haircut on the Austrian estimate, allowing for Switzerland's higher rights value per capita, and escalates 4%. Low confidence but small: a 50% error moves the total by about 0.3%.</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR service announcements; F1 broadcaster directory. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -4742,7 +5935,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Belgium</t>
         </is>
@@ -4768,16 +5961,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G13" s="222">
+      <c r="G13" s="258">
         <v>9</v>
       </c>
-      <c r="H13" s="222">
+      <c r="H13" s="258">
         <v>9.36</v>
       </c>
-      <c r="I13" s="222">
+      <c r="I13" s="258">
         <v>9.73</v>
       </c>
-      <c r="J13" s="222">
+      <c r="J13" s="258">
         <v>0</v>
       </c>
       <c r="K13" s="33" t="inlineStr">
@@ -4795,7 +5988,7 @@
           <t xml:space="preserve">No published fee in any Belgian source reviewed. $9m is an EST on a small-Euro peer basis, below the Czech and Hungarian rows despite the larger F1 footprint because Belgian rights are split free-to-air and pay. Low confidence, small weight.</t>
         </is>
       </c>
-      <c r="N13" s="12" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, RTBF extension through 2027; Telenet Play Sports renewal. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -4803,7 +5996,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
         </is>
@@ -4829,16 +6022,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G14" s="222">
+      <c r="G14" s="258">
         <v>83.35</v>
       </c>
-      <c r="H14" s="222">
+      <c r="H14" s="258">
         <v>86.69</v>
       </c>
-      <c r="I14" s="222">
+      <c r="I14" s="258">
         <v>90.15</v>
       </c>
-      <c r="J14" s="222">
+      <c r="J14" s="258">
         <v>93.76</v>
       </c>
       <c r="K14" s="33" t="inlineStr">
@@ -4856,7 +6049,7 @@
           <t xml:space="preserve">One row, two components merged: $63.7m is the EUR60m reported floor at about 1.08, and $19.6m is the incremental value implied by Canal+ describing the renewal as a significant increase, taken at the low end of a 25-50% uplift band. The source workbook carries those as two rows; merging them stops the uplift being read as a separate contract. A EUR90m reading circulating on an unverified student blog was rejected. Francophone Africa is inside this fee, so no separate Canal+ Afrique row exists.</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr">
+      <c r="N14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Equipe, April 2022: &gt;EUR60m a year for France plus Francophone Africa. RMC, Canal+ (Maxime Saada) on a significant increase. No combined figure published.
 https://corp.formula1.com/</t>
@@ -4864,7 +6057,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
         </is>
@@ -4890,16 +6083,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G15" s="222">
+      <c r="G15" s="258">
         <v>61.95</v>
       </c>
-      <c r="H15" s="222">
+      <c r="H15" s="258">
         <v>64.42</v>
       </c>
-      <c r="I15" s="222">
+      <c r="I15" s="258">
         <v>67</v>
       </c>
-      <c r="J15" s="222">
+      <c r="J15" s="258">
         <v>69.68</v>
       </c>
       <c r="K15" s="33" t="inlineStr">
@@ -4917,7 +6110,7 @@
           <t xml:space="preserve">Split at about $60m Spain plus $7m Portugal, escalated 4%. Deliberately above the EUR45m Telefonica reference and the EUR40-50m Spanish band because DAZN took exclusivity and added Portugal. A buy-side note puts combined Spain, Germany and Italy at about $250m against roughly $183m booked across those rows; the rows were not re-based to close that gap, and the source file's $192m proxy row is excluded for the same reason.</t>
         </is>
       </c>
-      <c r="N15" s="12" t="inlineStr">
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and DAZN, 8 Sep 2026 (term). Fee: 2Playbook, Spain EUR40-50m; prior Telefonica face ~EUR45m.
 https://corp.formula1.com/</t>
@@ -4925,7 +6118,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Netherlands &amp; Nordics</t>
         </is>
@@ -4951,16 +6144,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G16" s="222">
+      <c r="G16" s="258">
         <v>45.3</v>
       </c>
-      <c r="H16" s="222">
+      <c r="H16" s="258">
         <v>47.12</v>
       </c>
-      <c r="I16" s="222">
+      <c r="I16" s="258">
         <v>49</v>
       </c>
-      <c r="J16" s="222">
+      <c r="J16" s="258">
         <v>50.96</v>
       </c>
       <c r="K16" s="33" t="inlineStr">
@@ -4978,7 +6171,7 @@
           <t xml:space="preserve">Sportcal reported the combined package at about $47m a year, so $49m sits just inside that print, with the Netherlands driving most of it. Escalated 4%. The step from roughly $30m for the Netherlands alone is one of the steeper renewal uplifts in the book.</t>
         </is>
       </c>
-      <c r="N16" s="12" t="inlineStr">
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, NL plus Nordics package ~$47m a year; NOS, Telegraaf and TotaalTV on the Dutch EUR45m component.
 https://corp.formula1.com/</t>
@@ -4986,7 +6179,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Poland</t>
         </is>
@@ -5012,16 +6205,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G17" s="222">
+      <c r="G17" s="258">
         <v>16.03</v>
       </c>
-      <c r="H17" s="222">
+      <c r="H17" s="258">
         <v>16.67</v>
       </c>
-      <c r="I17" s="222">
+      <c r="I17" s="258">
         <v>17.34</v>
       </c>
-      <c r="J17" s="222">
+      <c r="J17" s="258">
         <v>18.03</v>
       </c>
       <c r="K17" s="33" t="inlineStr">
@@ -5039,7 +6232,7 @@
           <t xml:space="preserve">Cyfrowy Polsat's announcement described a record fee without a number, so $17m is the prior Viaplay cycle (about $15m per GlobalData) plus an uplift for the record-fee language. Direction of travel is reliable, magnitude is not.</t>
         </is>
       </c>
-      <c r="N17" s="12" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Cyfrowy Polsat, 30 Oct 2024: exclusive 2025-28, record fee, no figure. Prior cycle ~$15m per GlobalData/Sportcal.
 https://grupapolsatplus.pl/en/archive/formula-1-back-eleven-sports-network-has-secured-exclusive-rights-next-four-seasons</t>
@@ -5047,7 +6240,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Hungary</t>
         </is>
@@ -5073,16 +6266,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G18" s="222">
+      <c r="G18" s="258">
         <v>13.67</v>
       </c>
-      <c r="H18" s="222">
+      <c r="H18" s="258">
         <v>14.22</v>
       </c>
-      <c r="I18" s="222">
+      <c r="I18" s="258">
         <v>14.79</v>
       </c>
-      <c r="J18" s="222">
+      <c r="J18" s="258">
         <v>15.38</v>
       </c>
       <c r="K18" s="33" t="inlineStr">
@@ -5100,7 +6293,7 @@
           <t xml:space="preserve">$14.5m a year derives from the reported $43.39m three-year prior package, escalated 4%; the 2026-27 renewal fee is undisclosed. MTVA pays through Hungaroring Sport, the race promoter, so the amount reaching F1 is at or below this face value.</t>
         </is>
       </c>
-      <c r="N18" s="12" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Magyar Hang, prior package $43.39m over 2023-25; MTI, December 2025 renewal through 2027.
 https://corp.formula1.com/</t>
@@ -5108,7 +6301,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Czechia &amp; Slovakia</t>
         </is>
@@ -5134,16 +6327,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G19" s="222">
+      <c r="G19" s="258">
         <v>5.77</v>
       </c>
-      <c r="H19" s="222">
+      <c r="H19" s="258">
         <v>6</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="258">
         <v>6.24</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="258">
         <v>6.49</v>
       </c>
       <c r="K19" s="33" t="inlineStr">
@@ -5161,7 +6354,7 @@
           <t xml:space="preserve">No published fee in either cycle. $6m is a population and GDP haircut on the Polish and Hungarian rows, escalated 4%. A 50% error moves the total by 0.2%.</t>
         </is>
       </c>
-      <c r="N19" s="12" t="inlineStr">
+      <c r="N19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nova Sport launch announcements; F1 broadcaster directory. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -5169,7 +6362,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Rest of Europe &amp; Israel</t>
         </is>
@@ -5197,16 +6390,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G20" s="222">
+      <c r="G20" s="258">
         <v>10.58</v>
       </c>
-      <c r="H20" s="222">
+      <c r="H20" s="258">
         <v>11</v>
       </c>
-      <c r="I20" s="222">
+      <c r="I20" s="258">
         <v>11.44</v>
       </c>
-      <c r="J20" s="222">
+      <c r="J20" s="258">
         <v>11.9</v>
       </c>
       <c r="K20" s="33" t="inlineStr">
@@ -5224,7 +6417,7 @@
           <t xml:space="preserve">Long-tail basket carried at about $11m, built bottom-up at roughly EUR0.3-1.5m per market. Every constituent fee is unpublished. The Infront Balkans sublicence signed in June 2025 is the largest single piece.</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Infront, Balkans sublicence June 2025; F1 broadcaster directory for the constituent territories. All fees unpublished.
 https://corp.formula1.com/</t>
@@ -5232,7 +6425,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
         </is>
@@ -5258,16 +6451,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G21" s="222">
+      <c r="G21" s="258">
         <v>43.59</v>
       </c>
-      <c r="H21" s="222">
+      <c r="H21" s="258">
         <v>45.33</v>
       </c>
-      <c r="I21" s="222">
+      <c r="I21" s="258">
         <v>47.14</v>
       </c>
-      <c r="J21" s="222">
+      <c r="J21" s="258">
         <v>49.03</v>
       </c>
       <c r="K21" s="33" t="inlineStr">
@@ -5285,7 +6478,7 @@
           <t xml:space="preserve">$50m a year is the $500m-plus ten-year print divided down, escalated 4%, so early years sit below the term average. It is a face-value figure that may be gross of production or marketing commitments in a way the European rows are not, which is why it is not treated as directly comparable.</t>
         </is>
       </c>
-      <c r="N21" s="12" t="inlineStr">
+      <c r="N21" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Bloomberg and Reuters, November 2023: &gt;$500m over ten years.
 https://corp.formula1.com/</t>
@@ -5293,7 +6486,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia (10 territories) — beIN</t>
         </is>
@@ -5319,16 +6512,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G22" s="222">
+      <c r="G22" s="258">
         <v>22.22</v>
       </c>
-      <c r="H22" s="222">
+      <c r="H22" s="258">
         <v>23.11</v>
       </c>
-      <c r="I22" s="222">
+      <c r="I22" s="258">
         <v>24.04</v>
       </c>
-      <c r="J22" s="222">
+      <c r="J22" s="258">
         <v>25</v>
       </c>
       <c r="K22" s="33" t="inlineStr">
@@ -5346,7 +6539,7 @@
           <t xml:space="preserve">Set at roughly 0.3-0.8x the MENA value, scaled down for a far lower per-capita rights market. beIN's own release cites double-digit audience growth in the region, supporting a renewal at or above the prior fee. No trade print for either cycle. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and beIN, February 2026 (term, no fee); Liberty Media Q1 2026 commentary on the pan-Asia extension.
 https://corp.formula1.com/</t>
@@ -5354,7 +6547,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sub-Saharan Africa</t>
         </is>
@@ -5382,16 +6575,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G23" s="222">
+      <c r="G23" s="258">
         <v>9.62</v>
       </c>
-      <c r="H23" s="222">
+      <c r="H23" s="258">
         <v>10</v>
       </c>
-      <c r="I23" s="222">
+      <c r="I23" s="258">
         <v>10.4</v>
       </c>
-      <c r="J23" s="222">
+      <c r="J23" s="258">
         <v>10.82</v>
       </c>
       <c r="K23" s="33" t="inlineStr">
@@ -5409,7 +6602,7 @@
           <t xml:space="preserve">MultiChoice's annual report does not isolate an F1 line and SportBusiness reported the fee as broadly steady in 2020, so $10m is directional. The continent is split by language: this row covers English-speaking Africa, Canal+ covers Francophone Africa, with no overlap.</t>
         </is>
       </c>
-      <c r="N23" s="12" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">SportBusiness, 2020: SuperSport fee steady. MultiChoice annual report, no F1 isolate.
 https://corp.formula1.com/</t>
@@ -5417,7 +6610,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Japan</t>
         </is>
@@ -5443,16 +6636,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G24" s="222">
+      <c r="G24" s="258">
         <v>19.56</v>
       </c>
-      <c r="H24" s="222">
+      <c r="H24" s="258">
         <v>20.34</v>
       </c>
-      <c r="I24" s="222">
+      <c r="I24" s="258">
         <v>21.15</v>
       </c>
-      <c r="J24" s="222">
+      <c r="J24" s="258">
         <v>22</v>
       </c>
       <c r="K24" s="33" t="inlineStr">
@@ -5470,7 +6663,7 @@
           <t xml:space="preserve">F1's December 2025 announcement disclosed the term but not the fee. Sponichi's 'several-billion-yen' report brackets roughly $13-60m; $22m sits toward the top because the package is exclusive across all rights rather than split between pay and free-to-air as under DAZN. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Fuji TV, 4 Dec 2025 (term, no fee); Sponichi, tens-of-billions-of-yen scale.
 https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
@@ -5478,7 +6671,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">China</t>
         </is>
@@ -5504,16 +6697,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G25" s="222">
+      <c r="G25" s="258">
         <v>5</v>
       </c>
-      <c r="H25" s="222">
+      <c r="H25" s="258">
         <v>5.2</v>
       </c>
-      <c r="I25" s="222">
+      <c r="I25" s="258">
         <v>5.41</v>
       </c>
-      <c r="J25" s="222">
+      <c r="J25" s="258">
         <v>0</v>
       </c>
       <c r="K25" s="33" t="inlineStr">
@@ -5531,7 +6724,7 @@
           <t xml:space="preserve">Chinese rights have been priced very low historically: Tencent's prior bid was reported around $0.5m a year and a China Telecom non-exclusive deal around $1m. $5m assumes the exclusive digital-plus-free-to-air stack repriced well above that micro floor. A $110m figure circulating on a rights blog was rejected as inconsistent with every audit trail in the market.</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
+      <c r="N25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Tencent renewal, term through 2027 (no fee); Lanxiong Sports on historic Chinese right values.
 https://corp.formula1.com/</t>
@@ -5539,7 +6732,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">India, Bangladesh, Nepal &amp; Sri Lanka</t>
         </is>
@@ -5565,16 +6758,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G26" s="222">
+      <c r="G26" s="258">
         <v>4.81</v>
       </c>
-      <c r="H26" s="222">
+      <c r="H26" s="258">
         <v>5</v>
       </c>
-      <c r="I26" s="222">
+      <c r="I26" s="258">
         <v>5.2</v>
       </c>
-      <c r="J26" s="222">
+      <c r="J26" s="258">
         <v>5.41</v>
       </c>
       <c r="K26" s="33" t="inlineStr">
@@ -5592,7 +6785,7 @@
           <t xml:space="preserve">FanCode sells a season pass at INR599, which caps what the market bears. No fee published in either cycle and SportBusiness characterised the deal as market value for digital-only rights, so $5m is directional and low confidence.</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
+      <c r="N26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and FanCode, December 2025 (term, no fee); SportBusiness on digital-only market value.
 https://corp.formula1.com/</t>
@@ -5600,7 +6793,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Korea, Chinese Taipei &amp; residual SE Asia</t>
         </is>
@@ -5626,16 +6819,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G27" s="222">
+      <c r="G27" s="258">
         <v>4.33</v>
       </c>
-      <c r="H27" s="222">
+      <c r="H27" s="258">
         <v>4.5</v>
       </c>
-      <c r="I27" s="222">
+      <c r="I27" s="258">
         <v>4.68</v>
       </c>
-      <c r="J27" s="222">
+      <c r="J27" s="258">
         <v>4.87</v>
       </c>
       <c r="K27" s="33" t="inlineStr">
@@ -5653,7 +6846,7 @@
           <t xml:space="preserve">No value published for any deal in this basket, so $4.5m is a residual sized between the Indian and Vietnamese rows. The least-supported line in the book and the first candidate for revision if any single fee surfaces.</t>
         </is>
       </c>
-      <c r="N27" s="12" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play extension, September 2025; ELTA Chinese Taipei through 2029. Fees unpublished.
 https://corp.formula1.com/</t>
@@ -5661,7 +6854,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Australia</t>
         </is>
@@ -5687,16 +6880,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G28" s="222">
+      <c r="G28" s="258">
         <v>31.2</v>
       </c>
-      <c r="H28" s="222">
+      <c r="H28" s="258">
         <v>32.45</v>
       </c>
-      <c r="I28" s="222">
+      <c r="I28" s="258">
         <v>42</v>
       </c>
-      <c r="J28" s="222">
+      <c r="J28" s="258">
         <v>43.68</v>
       </c>
       <c r="K28" s="33" t="inlineStr">
@@ -5714,7 +6907,7 @@
           <t xml:space="preserve">A$45m escalated 4% gives $31.2m for 2025 and $32.45m for 2026; the new deal converts A$60m at about 0.70 to $42m in 2027, escalated 4%. The source workbook splits this into two rows and books the new deal only in 2028; merging them avoids a gap year and a duplicate. Unlike most rows the 2027 step is a trade print on an actual contracted value rather than an estimate of an undisclosed sum.</t>
         </is>
       </c>
-      <c r="N28" s="12" t="inlineStr">
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sydney Morning Herald, A$45m a year for the incumbents; Formula 1, Kayo and Foxtel new deal announced 2026, A$60m a year from 2027.
 https://corp.formula1.com/</t>
@@ -5722,7 +6915,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">New Zealand</t>
         </is>
@@ -5748,16 +6941,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G29" s="222">
+      <c r="G29" s="258">
         <v>2.77</v>
       </c>
-      <c r="H29" s="222">
+      <c r="H29" s="258">
         <v>2.88</v>
       </c>
-      <c r="I29" s="222">
+      <c r="I29" s="258">
         <v>3</v>
       </c>
-      <c r="J29" s="222">
+      <c r="J29" s="258">
         <v>3.12</v>
       </c>
       <c r="K29" s="33" t="inlineStr">
@@ -5775,7 +6968,7 @@
           <t xml:space="preserve">Prior history is about $1.5m a year. $3m reflects the Lawson-era uplift in New Zealand interest plus 4% escalation. No published fee in either cycle. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N29" s="12" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky New Zealand, September 2025 three-year renewal (no fee); Coliseum history ~$1.5m a year.
 https://corp.formula1.com/</t>
@@ -5783,7 +6976,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Vietnam</t>
         </is>
@@ -5809,16 +7002,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G30" s="222">
+      <c r="G30" s="258">
         <v>0</v>
       </c>
-      <c r="H30" s="222">
+      <c r="H30" s="258">
         <v>1.92</v>
       </c>
-      <c r="I30" s="222">
+      <c r="I30" s="258">
         <v>2</v>
       </c>
-      <c r="J30" s="222">
+      <c r="J30" s="258">
         <v>2.08</v>
       </c>
       <c r="K30" s="33" t="inlineStr">
@@ -5836,7 +7029,7 @@
           <t xml:space="preserve">New market entry with no published fee and no predecessor to anchor on. $2m is a floor estimate for a single-country streaming deal, with wide error bars.</t>
         </is>
       </c>
-      <c r="N30" s="12" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">VOV, TV360 exclusive 2026-28. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -5844,7 +7037,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Global in-flight and in-ship</t>
         </is>
@@ -5872,16 +7065,16 @@
           <t xml:space="preserve">EST</t>
         </is>
       </c>
-      <c r="G31" s="222">
+      <c r="G31" s="258">
         <v>1.44</v>
       </c>
-      <c r="H31" s="222">
+      <c r="H31" s="258">
         <v>1.5</v>
       </c>
-      <c r="I31" s="222">
+      <c r="I31" s="258">
         <v>1.56</v>
       </c>
-      <c r="J31" s="222">
+      <c r="J31" s="258">
         <v>1.62</v>
       </c>
       <c r="K31" s="33" t="inlineStr">
@@ -5899,7 +7092,7 @@
           <t xml:space="preserve">Micro deal with no published value, sized at $1.5m against the New Zealand and Vietnam rows. Immaterial to the total but included so the territory list matches F1's own broadcaster directory.</t>
         </is>
       </c>
-      <c r="N31" s="12" t="inlineStr">
+      <c r="N31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 broadcaster directory, in-ship and in-flight listing. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -5907,7 +7100,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -5935,16 +7128,16 @@
           <t xml:space="preserve">ASSUMP</t>
         </is>
       </c>
-      <c r="G32" s="222">
+      <c r="G32" s="258">
         <v>421.85</v>
       </c>
-      <c r="H32" s="222">
+      <c r="H32" s="258">
         <v>421.85</v>
       </c>
-      <c r="I32" s="222">
+      <c r="I32" s="258">
         <v>421.85</v>
       </c>
-      <c r="J32" s="222">
+      <c r="J32" s="258">
         <v>421.85</v>
       </c>
       <c r="K32" s="33" t="inlineStr">
@@ -5962,7 +7155,7 @@
           <t xml:space="preserve">This is the arithmetic gap that makes the named rows tie to the reported total, not a partner fee. 2025 is Liberty's reported $1,212.25m minus every other included row, held flat in dollars thereafter. Flat rather than escalated on purpose: escalating a residual this large would manufacture roughly $15m a year of revenue F1 has not guided to. Forward growth in the book therefore comes only from named deals. Read it as a reconciliation line, not a contract.</t>
         </is>
       </c>
-      <c r="N32" s="12" t="inlineStr">
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A and revenue note: media rights fees from licensing broadcast of F1 Events and F2/F3 races, F1 TV subscriptions, origination and archive footage, radio and other ancillary media rights.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -5970,39 +7163,35 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT IN TOTAL (expired or one-off)</t>
         </is>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
+      <c r="B33" s="15">
+        <v>0</v>
+      </c>
+      <c r="C33" s="15">
+        <v>0</v>
+      </c>
+      <c r="D33" s="33">
+        <v>0</v>
+      </c>
+      <c r="E33" s="33">
+        <v>0</v>
+      </c>
       <c r="F33" s="33"/>
-      <c r="G33" s="222">
-        <v>0</v>
-      </c>
-      <c r="H33" s="222">
-        <v>0</v>
-      </c>
-      <c r="I33" s="222">
-        <v>0</v>
-      </c>
-      <c r="J33" s="222">
-        <v>0</v>
-      </c>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
       <c r="K33" s="33"/>
-      <c r="L33" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shown for completeness and excluded from the total at the bottom of the sheet.</t>
-        </is>
-      </c>
+      <c r="L33" s="15"/>
       <c r="M33" s="15"/>
-      <c r="N33" s="12"/>
+      <c r="N33" s="14"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
@@ -6028,16 +7217,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G34" s="222">
+      <c r="G34" s="258">
         <v>87.5</v>
       </c>
-      <c r="H34" s="222">
+      <c r="H34" s="258">
         <v>0</v>
       </c>
-      <c r="I34" s="222">
+      <c r="I34" s="258">
         <v>0</v>
       </c>
-      <c r="J34" s="222">
+      <c r="J34" s="258">
         <v>0</v>
       </c>
       <c r="K34" s="33" t="inlineStr">
@@ -6055,7 +7244,7 @@
           <t xml:space="preserve">Retained so the 2025 mix is visible: Apple's $131.5m against ESPN's $87.5m is roughly a 50% increase, the largest single-deal uplift in the period. Excluded from every total.</t>
         </is>
       </c>
-      <c r="N34" s="12" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Sports Business Journal, June 2023: ESPN ~$87.5m a year.
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
@@ -6063,7 +7252,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Brazil</t>
         </is>
@@ -6089,16 +7278,16 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G35" s="222">
+      <c r="G35" s="258">
         <v>15</v>
       </c>
-      <c r="H35" s="222">
+      <c r="H35" s="258">
         <v>0</v>
       </c>
-      <c r="I35" s="222">
+      <c r="I35" s="258">
         <v>0</v>
       </c>
-      <c r="J35" s="222">
+      <c r="J35" s="258">
         <v>0</v>
       </c>
       <c r="K35" s="33" t="inlineStr">
@@ -6116,7 +7305,7 @@
           <t xml:space="preserve">Carried for continuity only. Folha's $15m print is the reference that shows how far Globo's fee fell.</t>
         </is>
       </c>
-      <c r="N35" s="12" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Folha de S.Paulo, Band ~$15m a year.
 https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
@@ -6124,7 +7313,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -6150,16 +7339,16 @@
           <t xml:space="preserve">HARD</t>
         </is>
       </c>
-      <c r="G36" s="222">
+      <c r="G36" s="258">
         <v>15</v>
       </c>
-      <c r="H36" s="222">
+      <c r="H36" s="258">
         <v>0</v>
       </c>
-      <c r="I36" s="222">
+      <c r="I36" s="258">
         <v>0</v>
       </c>
-      <c r="J36" s="222">
+      <c r="J36" s="258">
         <v>0</v>
       </c>
       <c r="K36" s="33" t="inlineStr">
@@ -6177,7 +7366,7 @@
           <t xml:space="preserve">Liberty's FY2025 MD&amp;A cites one-time revenue from the film release in explaining media rights growth. Booked at $15m in 2025 only; including it would overstate the 2026 base.</t>
         </is>
       </c>
-      <c r="N36" s="12" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A: one-time revenue associated with the release of the F1 movie.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -6190,31 +7379,3779 @@
           <t xml:space="preserve">RECONCILED TOTAL (included rows)</t>
         </is>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="223">
+      <c r="B37" s="17">
         <v>1212.25</v>
       </c>
-      <c r="H37" s="223">
+      <c r="C37" s="17">
         <v>1418.76</v>
       </c>
-      <c r="I37" s="223">
+      <c r="D37" s="35">
         <v>1459.1</v>
       </c>
-      <c r="J37" s="223">
+      <c r="E37" s="35">
         <v>1477.09</v>
       </c>
-      <c r="K37" s="34"/>
-      <c r="L37" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ties to Liberty's reported FY2025 F1 media rights revenue of $1,212.25m. 2026-28 have no reported comparator.</t>
-        </is>
-      </c>
-      <c r="M37" s="16"/>
-      <c r="N37" s="14"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="260"/>
+      <c r="H37" s="260"/>
+      <c r="I37" s="260"/>
+      <c r="J37" s="260"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="11"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="42.00" customWidth="1"/>
+    <col min="2" max="2" width="30.00" customWidth="1"/>
+    <col min="3" max="3" width="12.00" customWidth="1"/>
+    <col min="4" max="4" width="8.00" customWidth="1"/>
+    <col min="5" max="5" width="8.00" customWidth="1"/>
+    <col min="6" max="6" width="10.00" customWidth="1"/>
+    <col min="7" max="7" width="13.00" customWidth="1"/>
+    <col min="8" max="8" width="13.00" customWidth="1"/>
+    <col min="9" max="9" width="12.00" customWidth="1"/>
+    <col min="10" max="10" width="10.00" customWidth="1"/>
+    <col min="11" max="11" width="10.00" customWidth="1"/>
+    <col min="12" max="12" width="12.00" customWidth="1"/>
+    <col min="13" max="13" width="13.00" customWidth="1"/>
+    <col min="14" max="14" width="80.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Rights Holder</t>
+        </is>
+      </c>
+      <c r="B1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="C1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Term</t>
+        </is>
+      </c>
+      <c r="D1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Total</t>
+        </is>
+      </c>
+      <c r="F1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Type</t>
+        </is>
+      </c>
+      <c r="G1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025 (USD m)</t>
+        </is>
+      </c>
+      <c r="H1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026 (USD m)</t>
+        </is>
+      </c>
+      <c r="I1" s="601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delta (USD m)</t>
+        </is>
+      </c>
+      <c r="J1" s="709" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delta %</t>
+        </is>
+      </c>
+      <c r="K1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelled?</t>
+        </is>
+      </c>
+      <c r="L1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Range low (USD m)</t>
+        </is>
+      </c>
+      <c r="M1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Range high (USD m)</t>
+        </is>
+      </c>
+      <c r="N1" s="99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What's changing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— STEP-UP —</t>
+        </is>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="438"/>
+      <c r="H2" s="438"/>
+      <c r="I2" s="546"/>
+      <c r="J2" s="654"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="438"/>
+      <c r="M2" s="438"/>
+      <c r="N2" s="50"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
+        </is>
+      </c>
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2025</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="G3" s="438">
+        <v>87.5</v>
+      </c>
+      <c r="H3" s="438">
+        <v>0</v>
+      </c>
+      <c r="I3" s="546">
+        <v>-87.5</v>
+      </c>
+      <c r="J3" s="654">
+        <v>-1</v>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L3" s="438"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Band</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="G4" s="438">
+        <v>15</v>
+      </c>
+      <c r="H4" s="438">
+        <v>0</v>
+      </c>
+      <c r="I4" s="546">
+        <v>-15</v>
+      </c>
+      <c r="J4" s="654">
+        <v>-1</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L4" s="438"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 movie (Brad Pitt)</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HARD</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="G5" s="438">
+        <v>15</v>
+      </c>
+      <c r="H5" s="438">
+        <v>0</v>
+      </c>
+      <c r="I5" s="546">
+        <v>-15</v>
+      </c>
+      <c r="J5" s="654">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L5" s="438"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2032</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="G6" s="438">
+        <v>28.85</v>
+      </c>
+      <c r="H6" s="438">
+        <v>30</v>
+      </c>
+      <c r="I6" s="546">
+        <v>1.15</v>
+      </c>
+      <c r="J6" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L6" s="438"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 deals</t>
+        </is>
+      </c>
+      <c r="C7" s="6">
+        <v>-116.35</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="438"/>
+      <c r="H7" s="438"/>
+      <c r="I7" s="546"/>
+      <c r="J7" s="654"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— NEW DEAL —</t>
+        </is>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="438"/>
+      <c r="H8" s="438"/>
+      <c r="I8" s="546"/>
+      <c r="J8" s="654"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="438"/>
+      <c r="M8" s="438"/>
+      <c r="N8" s="50"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G9" s="438">
+        <v>0</v>
+      </c>
+      <c r="H9" s="438">
+        <v>131.52</v>
+      </c>
+      <c r="I9" s="546">
+        <v>131.52</v>
+      </c>
+      <c r="J9" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L9" s="438"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G10" s="438">
+        <v>0</v>
+      </c>
+      <c r="H10" s="438">
+        <v>35</v>
+      </c>
+      <c r="I10" s="546">
+        <v>35</v>
+      </c>
+      <c r="J10" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L10" s="438">
+        <v>25</v>
+      </c>
+      <c r="M10" s="438">
+        <v>45</v>
+      </c>
+      <c r="N10" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First year of the 2026-28 LatAm/Caribbean cycle inside the wider Disney agreement. Estimated: the previous cycle was not split out, so no prior-year figure exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G11" s="438">
+        <v>0</v>
+      </c>
+      <c r="H11" s="438">
+        <v>8</v>
+      </c>
+      <c r="I11" s="546">
+        <v>8</v>
+      </c>
+      <c r="J11" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L11" s="438"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV360 (Viettel)</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vietnam</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G12" s="438">
+        <v>0</v>
+      </c>
+      <c r="H12" s="438">
+        <v>1.92</v>
+      </c>
+      <c r="I12" s="546">
+        <v>1.92</v>
+      </c>
+      <c r="J12" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L12" s="438">
+        <v>1.5</v>
+      </c>
+      <c r="M12" s="438">
+        <v>2.5</v>
+      </c>
+      <c r="N12" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Vietnam entry from 2026. Estimated: no public fee; sized at $2m as a small-population first cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G13" s="438">
+        <v>0</v>
+      </c>
+      <c r="H13" s="438">
+        <v>20.34</v>
+      </c>
+      <c r="I13" s="546">
+        <v>20.34</v>
+      </c>
+      <c r="J13" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L13" s="438">
+        <v>15</v>
+      </c>
+      <c r="M13" s="438">
+        <v>25</v>
+      </c>
+      <c r="N13" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclusive Japanese deal 2026-30 replacing the prior shared arrangement. Estimated at ~$20m a year, consistent with Japan sitting just below the beIN Asia package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korea, Chinese Taipei &amp; residual SE Asia</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2029</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G14" s="438">
+        <v>0</v>
+      </c>
+      <c r="H14" s="438">
+        <v>4.5</v>
+      </c>
+      <c r="I14" s="546">
+        <v>4.5</v>
+      </c>
+      <c r="J14" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L14" s="438">
+        <v>3.5</v>
+      </c>
+      <c r="M14" s="438">
+        <v>6</v>
+      </c>
+      <c r="N14" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korea, Chinese Taipei and residual South-East Asia re-contracted from 2026 as one package. Estimated at ~$4.5m a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sport New Zealand</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Zealand</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G15" s="438">
+        <v>0</v>
+      </c>
+      <c r="H15" s="438">
+        <v>3</v>
+      </c>
+      <c r="I15" s="546">
+        <v>3</v>
+      </c>
+      <c r="J15" s="654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L15" s="438">
+        <v>2</v>
+      </c>
+      <c r="M15" s="438">
+        <v>4</v>
+      </c>
+      <c r="N15" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Zealand renews for 2026-28. Estimated at ~$3m a year for a two-island market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 deals</t>
+        </is>
+      </c>
+      <c r="C16" s="6">
+        <v>177.5</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="438"/>
+      <c r="H16" s="438"/>
+      <c r="I16" s="546"/>
+      <c r="J16" s="654"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— ESCALATOR —</t>
+        </is>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="438"/>
+      <c r="H17" s="438"/>
+      <c r="I17" s="546"/>
+      <c r="J17" s="654"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="438"/>
+      <c r="M17" s="438"/>
+      <c r="N17" s="50"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom, Ireland &amp; Italy</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2034</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G18" s="438">
+        <v>117</v>
+      </c>
+      <c r="H18" s="438">
+        <v>120.51</v>
+      </c>
+      <c r="I18" s="546">
+        <v>3.51</v>
+      </c>
+      <c r="J18" s="654">
+        <v>0.03</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L18" s="438"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-2029</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G19" s="438">
+        <v>81.87</v>
+      </c>
+      <c r="H19" s="438">
+        <v>85.15</v>
+      </c>
+      <c r="I19" s="546">
+        <v>3.28</v>
+      </c>
+      <c r="J19" s="654">
+        <v>0.0401</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L19" s="438"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2030</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G20" s="438">
+        <v>61.95</v>
+      </c>
+      <c r="H20" s="438">
+        <v>64.42</v>
+      </c>
+      <c r="I20" s="546">
+        <v>2.47</v>
+      </c>
+      <c r="J20" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L20" s="438"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2027</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G21" s="438">
+        <v>55</v>
+      </c>
+      <c r="H21" s="438">
+        <v>57.2</v>
+      </c>
+      <c r="I21" s="546">
+        <v>2.2</v>
+      </c>
+      <c r="J21" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L21" s="438"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands &amp; Nordics</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2029</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G22" s="438">
+        <v>45.3</v>
+      </c>
+      <c r="H22" s="438">
+        <v>47.12</v>
+      </c>
+      <c r="I22" s="546">
+        <v>1.82</v>
+      </c>
+      <c r="J22" s="654">
+        <v>0.0402</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L22" s="438"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2033</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G23" s="438">
+        <v>43.59</v>
+      </c>
+      <c r="H23" s="438">
+        <v>45.33</v>
+      </c>
+      <c r="I23" s="546">
+        <v>1.74</v>
+      </c>
+      <c r="J23" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L23" s="438"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia (10 territories) — beIN</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G24" s="438">
+        <v>22.22</v>
+      </c>
+      <c r="H24" s="438">
+        <v>23.11</v>
+      </c>
+      <c r="I24" s="546">
+        <v>0.89</v>
+      </c>
+      <c r="J24" s="654">
+        <v>0.0401</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L24" s="438"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServusTV</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austria</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2029</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G25" s="438">
+        <v>16.64</v>
+      </c>
+      <c r="H25" s="438">
+        <v>17.31</v>
+      </c>
+      <c r="I25" s="546">
+        <v>0.67</v>
+      </c>
+      <c r="J25" s="654">
+        <v>0.0403</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L25" s="438"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports / Polsat</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poland</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G26" s="438">
+        <v>16.03</v>
+      </c>
+      <c r="H26" s="438">
+        <v>16.67</v>
+      </c>
+      <c r="I26" s="546">
+        <v>0.64</v>
+      </c>
+      <c r="J26" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L26" s="438"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G27" s="438">
+        <v>13.67</v>
+      </c>
+      <c r="H27" s="438">
+        <v>14.22</v>
+      </c>
+      <c r="I27" s="546">
+        <v>0.55</v>
+      </c>
+      <c r="J27" s="654">
+        <v>0.0402</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L27" s="438"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rest of Europe &amp; Israel</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-open</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G28" s="438">
+        <v>10.58</v>
+      </c>
+      <c r="H28" s="438">
+        <v>11</v>
+      </c>
+      <c r="I28" s="546">
+        <v>0.42</v>
+      </c>
+      <c r="J28" s="654">
+        <v>0.0397</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L28" s="438"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-open</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G29" s="438">
+        <v>9.62</v>
+      </c>
+      <c r="H29" s="438">
+        <v>10</v>
+      </c>
+      <c r="I29" s="546">
+        <v>0.38</v>
+      </c>
+      <c r="J29" s="654">
+        <v>0.0395</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L29" s="438"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSN / RDS (Bell Media)</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2035</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G30" s="438">
+        <v>8.77</v>
+      </c>
+      <c r="H30" s="438">
+        <v>9.12</v>
+      </c>
+      <c r="I30" s="546">
+        <v>0.35</v>
+      </c>
+      <c r="J30" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L30" s="438"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRG SSR</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switzerland</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2018-open</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G31" s="438">
+        <v>7.69</v>
+      </c>
+      <c r="H31" s="438">
+        <v>8</v>
+      </c>
+      <c r="I31" s="546">
+        <v>0.31</v>
+      </c>
+      <c r="J31" s="654">
+        <v>0.0403</v>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L31" s="438"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G32" s="438">
+        <v>7.54</v>
+      </c>
+      <c r="H32" s="438">
+        <v>7.84</v>
+      </c>
+      <c r="I32" s="546">
+        <v>0.3</v>
+      </c>
+      <c r="J32" s="654">
+        <v>0.0398</v>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L32" s="438"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV Nova / Nova Sport</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Czechia &amp; Slovakia</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2028</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G33" s="438">
+        <v>5.77</v>
+      </c>
+      <c r="H33" s="438">
+        <v>6</v>
+      </c>
+      <c r="I33" s="546">
+        <v>0.23</v>
+      </c>
+      <c r="J33" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L33" s="438"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G34" s="438">
+        <v>5</v>
+      </c>
+      <c r="H34" s="438">
+        <v>5.2</v>
+      </c>
+      <c r="I34" s="546">
+        <v>0.2</v>
+      </c>
+      <c r="J34" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L34" s="438"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FanCode</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">India, Bangladesh, Nepal &amp; Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2028</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G35" s="438">
+        <v>4.81</v>
+      </c>
+      <c r="H35" s="438">
+        <v>5</v>
+      </c>
+      <c r="I35" s="546">
+        <v>0.19</v>
+      </c>
+      <c r="J35" s="654">
+        <v>0.0395</v>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L35" s="438"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global in-flight and in-ship</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-open</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G36" s="438">
+        <v>1.44</v>
+      </c>
+      <c r="H36" s="438">
+        <v>1.5</v>
+      </c>
+      <c r="I36" s="546">
+        <v>0.06</v>
+      </c>
+      <c r="J36" s="654">
+        <v>0.0417</v>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L36" s="438"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 deals</t>
+        </is>
+      </c>
+      <c r="C37" s="6">
+        <v>20.21</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="438"/>
+      <c r="H37" s="438"/>
+      <c r="I37" s="546"/>
+      <c r="J37" s="654"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="48"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="438"/>
+      <c r="H38" s="438"/>
+      <c r="I38" s="546"/>
+      <c r="J38" s="654"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="438"/>
+      <c r="M38" s="438"/>
+      <c r="N38" s="50"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">READ ACROSS</t>
+        </is>
+      </c>
+      <c r="B39" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 step-up / 7 new / 19 escalator rows</t>
+        </is>
+      </c>
+      <c r="C39" s="6"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOOK LEDGER</t>
+        </is>
+      </c>
+      <c r="B40" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calendar total 2026 less 2025, versus the rows above</t>
+        </is>
+      </c>
+      <c r="C40" s="6">
+        <v>1212.25</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="438"/>
+      <c r="H40" s="438">
+        <v>1411.11</v>
+      </c>
+      <c r="I40" s="546">
+        <v>198.86</v>
+      </c>
+      <c r="J40" s="654">
+        <v>0.164</v>
+      </c>
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total of listed rows</t>
+        </is>
+      </c>
+      <c r="B41" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 rows</t>
+        </is>
+      </c>
+      <c r="C41" s="8">
+        <v>81.36</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="440"/>
+      <c r="H41" s="440"/>
+      <c r="I41" s="548"/>
+      <c r="J41" s="656"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="42.00" customWidth="1"/>
+    <col min="2" max="2" width="30.00" customWidth="1"/>
+    <col min="3" max="3" width="12.00" customWidth="1"/>
+    <col min="4" max="4" width="8.00" customWidth="1"/>
+    <col min="5" max="5" width="8.00" customWidth="1"/>
+    <col min="6" max="6" width="10.00" customWidth="1"/>
+    <col min="7" max="7" width="13.00" customWidth="1"/>
+    <col min="8" max="8" width="13.00" customWidth="1"/>
+    <col min="9" max="9" width="12.00" customWidth="1"/>
+    <col min="10" max="10" width="10.00" customWidth="1"/>
+    <col min="11" max="11" width="10.00" customWidth="1"/>
+    <col min="12" max="12" width="12.00" customWidth="1"/>
+    <col min="13" max="13" width="13.00" customWidth="1"/>
+    <col min="14" max="14" width="80.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Rights Holder</t>
+        </is>
+      </c>
+      <c r="B1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="C1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Term</t>
+        </is>
+      </c>
+      <c r="D1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Total</t>
+        </is>
+      </c>
+      <c r="F1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Type</t>
+        </is>
+      </c>
+      <c r="G1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026 (USD m)</t>
+        </is>
+      </c>
+      <c r="H1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027 (USD m)</t>
+        </is>
+      </c>
+      <c r="I1" s="601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delta (USD m)</t>
+        </is>
+      </c>
+      <c r="J1" s="709" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delta %</t>
+        </is>
+      </c>
+      <c r="K1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelled?</t>
+        </is>
+      </c>
+      <c r="L1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Range low (USD m)</t>
+        </is>
+      </c>
+      <c r="M1" s="493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Range high (USD m)</t>
+        </is>
+      </c>
+      <c r="N1" s="99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What's changing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— STEP-UP —</t>
+        </is>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="438"/>
+      <c r="H2" s="438"/>
+      <c r="I2" s="546"/>
+      <c r="J2" s="654"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="438"/>
+      <c r="M2" s="438"/>
+      <c r="N2" s="50"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
+        </is>
+      </c>
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2032</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="G3" s="438">
+        <v>30</v>
+      </c>
+      <c r="H3" s="438">
+        <v>42</v>
+      </c>
+      <c r="I3" s="546">
+        <v>12</v>
+      </c>
+      <c r="J3" s="654">
+        <v>0.4</v>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L3" s="438"/>
+      <c r="M3" s="438"/>
+      <c r="N3" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Second Australian contract begins in 2027: ~A$45m steps to ~A$60m a year, a one-third uplift worth about +$12m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 deal</t>
+        </is>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="438"/>
+      <c r="H4" s="438"/>
+      <c r="I4" s="546">
+        <v>12</v>
+      </c>
+      <c r="J4" s="654"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="438"/>
+      <c r="M4" s="438"/>
+      <c r="N4" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal of the step-up rows above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— NEW DEAL —</t>
+        </is>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="438"/>
+      <c r="H5" s="438"/>
+      <c r="I5" s="546"/>
+      <c r="J5" s="654"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="438"/>
+      <c r="M5" s="438"/>
+      <c r="N5" s="50"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G6" s="438">
+        <v>131.52</v>
+      </c>
+      <c r="H6" s="438">
+        <v>138.1</v>
+      </c>
+      <c r="I6" s="546">
+        <v>6.58</v>
+      </c>
+      <c r="J6" s="654">
+        <v>0.05</v>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L6" s="438"/>
+      <c r="M6" s="438"/>
+      <c r="N6" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year 2 of the US deal at a 5% annual escalator, to the $145m 2028 level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G7" s="438">
+        <v>20.34</v>
+      </c>
+      <c r="H7" s="438">
+        <v>22</v>
+      </c>
+      <c r="I7" s="546">
+        <v>1.66</v>
+      </c>
+      <c r="J7" s="654">
+        <v>0.0816</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L7" s="438">
+        <v>15</v>
+      </c>
+      <c r="M7" s="438">
+        <v>25</v>
+      </c>
+      <c r="N7" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Second-year lift in the 2026-30 Japanese deal; escalates above the book rate. Modelled, not contracted in public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G8" s="438">
+        <v>35</v>
+      </c>
+      <c r="H8" s="438">
+        <v>36.4</v>
+      </c>
+      <c r="I8" s="546">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L8" s="438">
+        <v>25</v>
+      </c>
+      <c r="M8" s="438">
+        <v>45</v>
+      </c>
+      <c r="N8" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation in year 2 of the LatAm/Caribbean cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G9" s="438">
+        <v>8</v>
+      </c>
+      <c r="H9" s="438">
+        <v>8.32</v>
+      </c>
+      <c r="I9" s="546">
+        <v>0.32</v>
+      </c>
+      <c r="J9" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L9" s="438"/>
+      <c r="M9" s="438"/>
+      <c r="N9" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation in year 2 of the Brazilian deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korea, Chinese Taipei &amp; residual SE Asia</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2029</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G10" s="438">
+        <v>4.5</v>
+      </c>
+      <c r="H10" s="438">
+        <v>4.68</v>
+      </c>
+      <c r="I10" s="546">
+        <v>0.18</v>
+      </c>
+      <c r="J10" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L10" s="438">
+        <v>3.5</v>
+      </c>
+      <c r="M10" s="438">
+        <v>6</v>
+      </c>
+      <c r="N10" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation in year 2 of the re-contracted basket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sport New Zealand</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Zealand</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G11" s="438">
+        <v>2.88</v>
+      </c>
+      <c r="H11" s="438">
+        <v>3</v>
+      </c>
+      <c r="I11" s="546">
+        <v>0.12</v>
+      </c>
+      <c r="J11" s="654">
+        <v>0.0417</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L11" s="438">
+        <v>2</v>
+      </c>
+      <c r="M11" s="438">
+        <v>4</v>
+      </c>
+      <c r="N11" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation in year 2 of the New Zealand deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV360 (Viettel)</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vietnam</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="G12" s="438">
+        <v>1.92</v>
+      </c>
+      <c r="H12" s="438">
+        <v>2</v>
+      </c>
+      <c r="I12" s="546">
+        <v>0.08</v>
+      </c>
+      <c r="J12" s="654">
+        <v>0.0417</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est</t>
+        </is>
+      </c>
+      <c r="L12" s="438">
+        <v>1.5</v>
+      </c>
+      <c r="M12" s="438">
+        <v>2.5</v>
+      </c>
+      <c r="N12" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation in year 2 of the Vietnamese deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 deals</t>
+        </is>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="438"/>
+      <c r="H13" s="438"/>
+      <c r="I13" s="546">
+        <v>10.34</v>
+      </c>
+      <c r="J13" s="654"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="438"/>
+      <c r="M13" s="438"/>
+      <c r="N13" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal of the new deal rows above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— ESCALATOR —</t>
+        </is>
+      </c>
+      <c r="B14" s="51"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="438"/>
+      <c r="H14" s="438"/>
+      <c r="I14" s="546"/>
+      <c r="J14" s="654"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="438"/>
+      <c r="M14" s="438"/>
+      <c r="N14" s="50"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom, Ireland &amp; Italy</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2034</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G15" s="438">
+        <v>120.51</v>
+      </c>
+      <c r="H15" s="438">
+        <v>124.13</v>
+      </c>
+      <c r="I15" s="546">
+        <v>3.62</v>
+      </c>
+      <c r="J15" s="654">
+        <v>0.03</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L15" s="438"/>
+      <c r="M15" s="438"/>
+      <c r="N15" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3% contract rate, below the 4% book rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-2029</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G16" s="438">
+        <v>85.15</v>
+      </c>
+      <c r="H16" s="438">
+        <v>88.55</v>
+      </c>
+      <c r="I16" s="546">
+        <v>3.4</v>
+      </c>
+      <c r="J16" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L16" s="438"/>
+      <c r="M16" s="438"/>
+      <c r="N16" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2030</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G17" s="438">
+        <v>64.42</v>
+      </c>
+      <c r="H17" s="438">
+        <v>67</v>
+      </c>
+      <c r="I17" s="546">
+        <v>2.58</v>
+      </c>
+      <c r="J17" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L17" s="438"/>
+      <c r="M17" s="438"/>
+      <c r="N17" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2027</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G18" s="438">
+        <v>57.2</v>
+      </c>
+      <c r="H18" s="438">
+        <v>59.49</v>
+      </c>
+      <c r="I18" s="546">
+        <v>2.29</v>
+      </c>
+      <c r="J18" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L18" s="438"/>
+      <c r="M18" s="438"/>
+      <c r="N18" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation. Final year: Germany goes to a 2028 tender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands &amp; Nordics</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2029</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G19" s="438">
+        <v>47.12</v>
+      </c>
+      <c r="H19" s="438">
+        <v>49</v>
+      </c>
+      <c r="I19" s="546">
+        <v>1.88</v>
+      </c>
+      <c r="J19" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L19" s="438"/>
+      <c r="M19" s="438"/>
+      <c r="N19" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2033</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G20" s="438">
+        <v>45.33</v>
+      </c>
+      <c r="H20" s="438">
+        <v>47.14</v>
+      </c>
+      <c r="I20" s="546">
+        <v>1.81</v>
+      </c>
+      <c r="J20" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L20" s="438"/>
+      <c r="M20" s="438"/>
+      <c r="N20" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia (10 territories) — beIN</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G21" s="438">
+        <v>23.11</v>
+      </c>
+      <c r="H21" s="438">
+        <v>24.04</v>
+      </c>
+      <c r="I21" s="546">
+        <v>0.93</v>
+      </c>
+      <c r="J21" s="654">
+        <v>0.0402</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L21" s="438"/>
+      <c r="M21" s="438"/>
+      <c r="N21" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServusTV</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austria</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2029</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G22" s="438">
+        <v>17.31</v>
+      </c>
+      <c r="H22" s="438">
+        <v>18</v>
+      </c>
+      <c r="I22" s="546">
+        <v>0.69</v>
+      </c>
+      <c r="J22" s="654">
+        <v>0.0399</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L22" s="438"/>
+      <c r="M22" s="438"/>
+      <c r="N22" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation; free-to-air inventory rises to 13 races a year from 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports / Polsat</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poland</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G23" s="438">
+        <v>16.67</v>
+      </c>
+      <c r="H23" s="438">
+        <v>17.34</v>
+      </c>
+      <c r="I23" s="546">
+        <v>0.67</v>
+      </c>
+      <c r="J23" s="654">
+        <v>0.0402</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L23" s="438"/>
+      <c r="M23" s="438"/>
+      <c r="N23" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRADE</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G24" s="438">
+        <v>14.22</v>
+      </c>
+      <c r="H24" s="438">
+        <v>14.79</v>
+      </c>
+      <c r="I24" s="546">
+        <v>0.57</v>
+      </c>
+      <c r="J24" s="654">
+        <v>0.0401</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L24" s="438"/>
+      <c r="M24" s="438"/>
+      <c r="N24" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation. Final year; nothing is booked for 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rest of Europe &amp; Israel</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-open</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G25" s="438">
+        <v>11</v>
+      </c>
+      <c r="H25" s="438">
+        <v>11.44</v>
+      </c>
+      <c r="I25" s="546">
+        <v>0.44</v>
+      </c>
+      <c r="J25" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L25" s="438"/>
+      <c r="M25" s="438"/>
+      <c r="N25" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-open</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G26" s="438">
+        <v>10</v>
+      </c>
+      <c r="H26" s="438">
+        <v>10.4</v>
+      </c>
+      <c r="I26" s="546">
+        <v>0.4</v>
+      </c>
+      <c r="J26" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L26" s="438"/>
+      <c r="M26" s="438"/>
+      <c r="N26" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSN / RDS (Bell Media)</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2035</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G27" s="438">
+        <v>9.12</v>
+      </c>
+      <c r="H27" s="438">
+        <v>9.48</v>
+      </c>
+      <c r="I27" s="546">
+        <v>0.36</v>
+      </c>
+      <c r="J27" s="654">
+        <v>0.0395</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L27" s="438"/>
+      <c r="M27" s="438"/>
+      <c r="N27" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G28" s="438">
+        <v>7.84</v>
+      </c>
+      <c r="H28" s="438">
+        <v>8.16</v>
+      </c>
+      <c r="I28" s="546">
+        <v>0.32</v>
+      </c>
+      <c r="J28" s="654">
+        <v>0.0408</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L28" s="438"/>
+      <c r="M28" s="438"/>
+      <c r="N28" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRG SSR</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2018-open</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G29" s="438">
+        <v>8</v>
+      </c>
+      <c r="H29" s="438">
+        <v>8.32</v>
+      </c>
+      <c r="I29" s="546">
+        <v>0.32</v>
+      </c>
+      <c r="J29" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L29" s="438"/>
+      <c r="M29" s="438"/>
+      <c r="N29" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV Nova / Nova Sport</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Czechia &amp; Slovakia</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2028</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G30" s="438">
+        <v>6</v>
+      </c>
+      <c r="H30" s="438">
+        <v>6.24</v>
+      </c>
+      <c r="I30" s="546">
+        <v>0.24</v>
+      </c>
+      <c r="J30" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L30" s="438"/>
+      <c r="M30" s="438"/>
+      <c r="N30" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G31" s="438">
+        <v>5.2</v>
+      </c>
+      <c r="H31" s="438">
+        <v>5.41</v>
+      </c>
+      <c r="I31" s="546">
+        <v>0.21</v>
+      </c>
+      <c r="J31" s="654">
+        <v>0.0404</v>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L31" s="438"/>
+      <c r="M31" s="438"/>
+      <c r="N31" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation. Final year: China falls to zero in 2028 with no renewal in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FanCode</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">India, Bangladesh, Nepal &amp; Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2028</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G32" s="438">
+        <v>5</v>
+      </c>
+      <c r="H32" s="438">
+        <v>5.2</v>
+      </c>
+      <c r="I32" s="546">
+        <v>0.2</v>
+      </c>
+      <c r="J32" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L32" s="438"/>
+      <c r="M32" s="438"/>
+      <c r="N32" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global in-flight and in-ship</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-open</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="G33" s="438">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="438">
+        <v>1.56</v>
+      </c>
+      <c r="I33" s="546">
+        <v>0.06</v>
+      </c>
+      <c r="J33" s="654">
+        <v>0.04</v>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep</t>
+        </is>
+      </c>
+      <c r="L33" s="438"/>
+      <c r="M33" s="438"/>
+      <c r="N33" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 deals</t>
+        </is>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="438"/>
+      <c r="H34" s="438"/>
+      <c r="I34" s="546">
+        <v>20.99</v>
+      </c>
+      <c r="J34" s="654"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="438"/>
+      <c r="M34" s="438"/>
+      <c r="N34" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal of the escalator rows above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="438"/>
+      <c r="H35" s="438"/>
+      <c r="I35" s="546"/>
+      <c r="J35" s="654"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="438"/>
+      <c r="M35" s="438"/>
+      <c r="N35" s="50"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">READ ACROSS</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 step-up / 7 new / 19 escalator rows</t>
+        </is>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="438"/>
+      <c r="H36" s="438"/>
+      <c r="I36" s="546"/>
+      <c r="J36" s="654"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="438"/>
+      <c r="M36" s="438"/>
+      <c r="N36" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up +12.00, new deals +10.34, escalators +20.99. 18 of 19 escalator rows move at the 4% book rate; Sky UK at 3% is the exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOOK LEDGER</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calendar total 2027 less 2026, versus the rows above</t>
+        </is>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="438">
+        <v>1411.11</v>
+      </c>
+      <c r="H37" s="438">
+        <v>1454.44</v>
+      </c>
+      <c r="I37" s="546">
+        <v>43.33</v>
+      </c>
+      <c r="J37" s="654">
+        <v>0.0307</v>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="438"/>
+      <c r="M37" s="438"/>
+      <c r="N37" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows above sum to +43.33; the book moves +43.33. Nothing is unaccounted for in 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total of listed rows</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27 rows</t>
+        </is>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="440"/>
+      <c r="H38" s="440"/>
+      <c r="I38" s="548">
+        <v>43.33</v>
+      </c>
+      <c r="J38" s="656"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="440"/>
+      <c r="M38" s="440"/>
+      <c r="N38" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In-total movements only.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/MediaRightsOverview.xlsx
+++ b/MediaRightsOverview.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Media_Rights_Calendar" sheetId="6" r:id="rId6"/>
     <sheet name="2026 vs 2025" sheetId="7" r:id="rId7"/>
     <sheet name="2027 vs 2026" sheetId="8" r:id="rId8"/>
+    <sheet name="2025-2026_SUMMARY" sheetId="9" r:id="rId9"/>
+    <sheet name="2026-2027_SUMMARY" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -56,6 +58,15 @@
   </fills>
   <borders count="9">
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -89,10 +100,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -110,26 +121,8 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -140,6 +133,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2430,76 +2432,1146 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">Field</t>
         </is>
       </c>
-      <c r="B1" s="162" t="inlineStr">
+      <c r="B1" s="163" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="113" t="inlineStr">
+      <c r="B2" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Media Rights Overview</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="B3" s="113" t="inlineStr">
+      <c r="B3" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Media Rights.xlsx plus verified primary announcements</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Anchor</t>
         </is>
       </c>
-      <c r="B4" s="113" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K media rights revenue $1,212.25m</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Currency</t>
         </is>
       </c>
-      <c r="B5" s="113" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">USD millions</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Created</t>
         </is>
       </c>
-      <c r="B6" s="110" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="30.00" customWidth="1"/>
+    <col min="2" max="2" width="30.00" customWidth="1"/>
+    <col min="3" max="3" width="11.00" customWidth="1"/>
+    <col min="4" max="4" width="11.00" customWidth="1"/>
+    <col min="5" max="5" width="15.00" customWidth="1"/>
+    <col min="6" max="6" width="42.00" customWidth="1"/>
+    <col min="7" max="7" width="42.00" customWidth="1"/>
+    <col min="8" max="8" width="38.00" customWidth="1"/>
+    <col min="9" max="9" width="62.00" customWidth="1"/>
+    <col min="10" max="10" width="90.00" customWidth="1"/>
+    <col min="11" max="11" width="11.00" customWidth="1"/>
+    <col min="12" max="12" width="55.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Rights Holder</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="C1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Term</t>
+        </is>
+      </c>
+      <c r="D1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E1" s="602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Impact (USD m)</t>
+        </is>
+      </c>
+      <c r="F1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior Revenue in Region</t>
+        </is>
+      </c>
+      <c r="G1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New / Current Revenue in Region</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What's Changing</t>
+        </is>
+      </c>
+      <c r="I1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Notes</t>
+        </is>
+      </c>
+      <c r="K1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2032</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E2" s="546">
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incumbent contract, ~A$45m a year (~$30m)</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New contract from 2027, ~A$60m a year (~$42m)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-third step up as the new Australian contract starts</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Australian contract starts 2027 at ~A$60m/yr versus ~A$45m, a ~$12m step in dollars.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The clearest confirmed renewal step outside the US: ~A$45m goes to ~A$60m a year, both reported by the Sydney Morning Herald. F1 and Kayo confirmed the extension in Mar 2026 with no value, so the A$60m is a trade print, not a disclosure. Network 10 keeps the Australian GP free-to-air as a sublicence and pays Kayo, not F1. FX conversion (0.65 in, 0.70 out) adds to the dollar step.</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-and-kayo-sports-extend-multi-year-broadcast-deal-for-australia/
+https://www.sportcal.com/media/kayo-sports-retains-f1-rights-in-australia-network-10-to-remain-fta-partner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E3" s="546">
+        <v>6.6</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple, ~$131.5m in 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple, ~$138.1m in 2027</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5% escalator, year 2</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Second contract year lifts ~$131.5m to ~$138.1m on a modelled 5% escalator.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelled 5% step from the $131.5m 2026 start toward $145m in 2028, so the package totals roughly $750m. The contract is not a flat $140m a year. A 5% escalator on ~$131m is ~$6.6m, which is 77% of any plausible booking at the top of the range.</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/
+https://www.sportsbusinessjournal.com/Articles/2025/10/17/f1-apple-clinch-five-year-media-rights-deal-as-racing-series-pins-us-hopes-on-tech-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-2029</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E4" s="546">
+        <v>3.4</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+, ~$85.2m in 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+, ~$88.6m in 2027</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4% escalator</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% contract escalator; no event in 2027.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure contract escalator, no event in this window.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2030</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E5" s="546">
+        <v>2.6</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN, ~$64.4m in 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN, ~$67.0m in 2027</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4% escalator</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% contract escalator; the Iberia step landed in 2024.</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure contract escalator, no event in this window. The Iberia step happened at the 2024 award.</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands &amp; Nordics</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2029</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E6" s="546">
+        <v>1.9</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay, ~$47.1m in 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay, ~$49.0m in 2027</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4% escalator</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% contract escalator; the Dutch step landed in 2025.</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure contract escalator; the Dutch doubling landed in 2025.</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2033</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E7" s="546">
+        <v>1.8</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN, ~$45.3m in 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN, ~$47.1m in 2027</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4% escalator</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% contract escalator on a ten-year term.</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure contract escalator on a ten-year term.</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E8" s="546">
+        <v>1.7</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV, ~$20.3m in 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV, ~$22.0m in 2027</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Second-year lift, ~8% rather than 4%</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelled step from ~$20.3m to ~$22.0m, ~8% versus the ~4% book rate.</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The model steps Japan from $20.3m to $22.0m, double the book rate, with no public basis for the extra. Either the 2026 level is understated or the 2027 step is invented; both come from the same unspecified Sponichi bracket. Directional only.</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E9" s="546">
+        <v>1.4</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN, ~$35.0m in 2026 (EST)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN, ~$36.4m in 2027 (EST)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalator</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~4% escalator inside the 2026-28 cycle; no event in 2027.</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure escalator inside the 2026-28 cycle. Level is modelled; the step is not an event.</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia (10 territories)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E10" s="546">
+        <v>0.9</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Asia, ~$23.1m in 2026 (EST)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Asia, ~$24.0m in 2027 (EST)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4% escalator</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% escalator on an undisclosed renewal.</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure escalator on an undisclosed renewal.</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exit risk</t>
+        </is>
+      </c>
+      <c r="E11" s="546">
+        <v>0.6</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current cycle ~$14.2m in 2026, ends with 2027</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agreed through 2027 only; nothing booked for 2028</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract ends; 2028 unbooked</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract ends with 2027; nothing is booked for 2028.</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary expires at the end of 2027. The 2026-27 renewal was signed in Dec 2025 through 2027 only, and the model carries nothing for 2028. Small in dollars but it is a real unbooked renewal.</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E12" s="546">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo, ~$8.0m in 2026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo, ~$8.3m in 2027</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalator</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% escalator; the -$7m Band reset landed in 2026.</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure escalator. The -$7m Band-to-Globo reset landed in 2026 and does not repeat.</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escalator</t>
+        </is>
+      </c>
+      <c r="E13" s="546">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Televisa, ~$7.8m in 2026 (EST)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Televisa, ~$8.2m in 2027 (EST)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract escalator</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purely a ~4% escalator on ~$7.8m; the Fox exit landed in 2025-26.</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure escalator; the Fox Sports exit landed in 2025-26.</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exit risk</t>
+        </is>
+      </c>
+      <c r="E14" s="546">
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current cycle ~$5.2m in 2026, ends with 2027</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing booked for 2028</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract ends; no renewal announced</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract ends with 2027 with no renewal announced; the book falls to zero in 2028.</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China ends with 2027 and the book falls to zero in 2028. Given the historical micro-pricing of Chinese rights the renewal, if any, is unlikely to be larger. Flagged because a zero is a forecast here, not a fact.</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2037</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E15" s="546">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior UK/Ireland cycle, ~$84m a year</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New extension reportedly ~$125m a year; ~$87m in 2027 on the model path</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step is inside the reported ~GBP1bn package, not visible in the model</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step sits inside the reported ~GBP1bn package but is not visible in the blended UK/Italy row.</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same problem as 2026: the workbook carries one blended UK/Ireland/Italy row at a 3% escalator, which cannot show a contract step. The Sky extension was announced in May 2026 and reported at ~GBP1bn; whether any of that lands in 2027 as a step rather than a ramp is unknown. Left at zero so nothing is manufactured.</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No data</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-and-sky-agree-long-term-partnership-across-uk-ireland-and-italy/
+https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2027</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exit risk</t>
+        </is>
+      </c>
+      <c r="E16" s="546">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current cycle ~EUR50-55m a year, ends with 2027</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown - 2028 tender live under RTL ownership</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract ends; nothing booked for 2028</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rights expire end-2027 and nothing is booked for 2028; the tender is live.</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany expires at the end of 2027 and the model carries nothing for 2028. F1 has confirmed a competitive tender and Apple and Amazon have been named as interested, so the realistic outcomes for 2028 are a renewal above the current ~$60m or a new entrant. As it stands the book shows a ~$60m cliff in 2028 that is probably a placeholder rather than a forecast.</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No data</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports / Foxtel / Kayo (Network 10 sublicence)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2032</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural</t>
+        </is>
+      </c>
+      <c r="E17" s="546">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network 10 pays Kayo, not F1</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not F1 revenue</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network 10 buys the free-to-air window from Kayo, so it is not F1 revenue.</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Included so the Australia row is not read as containing the free-to-air money. Network 10's Australian GP window is a sublicence bought from Kayo.</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-and-kayo-sports-extend-multi-year-broadcast-deal-for-australia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NET CHANGE — rows above</t>
+        </is>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="547">
+        <v>33.7</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 entries. Directional, not additive: several rows are the same money counted once at contract level.</t>
+        </is>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="3"/>
     </row>
   </sheetData>
 </worksheet>
@@ -2520,54 +3592,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="61" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Term</t>
         </is>
       </c>
-      <c r="D1" s="61" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start</t>
         </is>
       </c>
-      <c r="E1" s="61" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Term End</t>
         </is>
       </c>
-      <c r="F1" s="61" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="G1" s="277" t="inlineStr">
+      <c r="G1" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">2028 Revenue (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="385" t="inlineStr">
+      <c r="H1" s="386" t="inlineStr">
         <is>
           <t xml:space="preserve">Share of 2028 Total</t>
         </is>
       </c>
-      <c r="I1" s="54" t="inlineStr">
+      <c r="I1" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">In 2028 Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (pooled residual) — F2/F3, archive, radio, ancillary</t>
         </is>
@@ -2601,14 +3673,14 @@
       <c r="H2" s="330">
         <v>0.25555445837859186</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -2642,14 +3714,14 @@
       <c r="H3" s="330">
         <v>0.11968006319739312</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -2681,14 +3753,14 @@
       <c r="H4" s="330">
         <v>0.09545439583950496</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -2720,14 +3792,14 @@
       <c r="H5" s="330">
         <v>0.08416444488331523</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -2759,14 +3831,14 @@
       <c r="H6" s="330">
         <v>0.0472005529771897</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -2798,14 +3870,14 @@
       <c r="H7" s="330">
         <v>0.045870774497218665</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -2837,14 +3909,14 @@
       <c r="H8" s="330">
         <v>0.04072940324544946</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -2876,14 +3948,14 @@
       <c r="H9" s="330">
         <v>0.033547282841249464</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -2915,14 +3987,14 @@
       <c r="H10" s="330">
         <v>0.03227675191731674</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Kayo Sports / Foxtel</t>
         </is>
@@ -2954,14 +4026,14 @@
       <c r="H11" s="330">
         <v>0.028754813863928114</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -2993,14 +4065,14 @@
       <c r="H12" s="330">
         <v>0.024923471906783845</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -3032,14 +4104,14 @@
       <c r="H13" s="330">
         <v>0.021526612027253877</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -3071,14 +4143,14 @@
       <c r="H14" s="330">
         <v>0.021362035482703007</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -3110,14 +4182,14 @@
       <c r="H15" s="330">
         <v>0.01645765445508706</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -3149,14 +4221,14 @@
       <c r="H16" s="330">
         <v>0.015075211480859748</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -3188,14 +4260,14 @@
       <c r="H17" s="330">
         <v>0.013429446035351041</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -3227,14 +4299,14 @@
       <c r="H18" s="330">
         <v>0.012323491655969191</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — other digital</t>
         </is>
@@ -3268,14 +4340,14 @@
       <c r="H19" s="330">
         <v>0.012244494914584774</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -3307,14 +4379,14 @@
       <c r="H20" s="330">
         <v>0.01186926039300879</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -3346,14 +4418,14 @@
       <c r="H21" s="330">
         <v>0.01012474902076956</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -3387,14 +4459,14 @@
       <c r="H22" s="330">
         <v>0.007833843520621442</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -3428,14 +4500,14 @@
       <c r="H23" s="330">
         <v>0.00712287284816168</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -3467,14 +4539,14 @@
       <c r="H24" s="330">
         <v>0.006490898917086337</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -3508,14 +4580,14 @@
       <c r="H25" s="330">
         <v>0.005694348441460124</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -3547,14 +4619,14 @@
       <c r="H26" s="330">
         <v>0.005582436391165532</v>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -3586,14 +4658,14 @@
       <c r="H27" s="330">
         <v>0.0054771074026529745</v>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -3625,14 +4697,14 @@
       <c r="H28" s="330">
         <v>0.004272407096540602</v>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -3664,14 +4736,14 @@
       <c r="H29" s="330">
         <v>0.0036996807215035716</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -3703,14 +4775,14 @@
       <c r="H30" s="330">
         <v>0.00356143642408084</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -3742,14 +4814,14 @@
       <c r="H31" s="330">
         <v>0.0032059510878509594</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -3781,14 +4853,14 @@
       <c r="H32" s="330">
         <v>0.0020539152759948653</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -3820,14 +4892,14 @@
       <c r="H33" s="330">
         <v>0.0013692768506632436</v>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -3861,14 +4933,14 @@
       <c r="H34" s="330">
         <v>0.0010664560086896416</v>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL</t>
         </is>
@@ -3900,7 +4972,7 @@
       <c r="H35" s="330"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ORF</t>
         </is>
@@ -3932,7 +5004,7 @@
       <c r="H36" s="330"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Band</t>
         </is>
@@ -3964,7 +5036,7 @@
       <c r="H37" s="330"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 movie (Brad Pitt)</t>
         </is>
@@ -3996,36 +5068,36 @@
       <c r="H38" s="330"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-2025</t>
         </is>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>2023</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="7">
         <v>2025</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G39" s="224">
+      <c r="G39" s="223">
         <v>0</v>
       </c>
-      <c r="H39" s="332"/>
+      <c r="H39" s="331"/>
     </row>
   </sheetData>
 </worksheet>
@@ -4041,29 +5113,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">Holder</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="70" t="inlineStr">
+      <c r="C1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">URLs Inspected</t>
         </is>
       </c>
-      <c r="D1" s="63" t="inlineStr">
+      <c r="D1" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">Named Citations (no public URL)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -4079,14 +5151,14 @@
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7 (Formula One Digital Media Ltd, subscription-based services $181.797m).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — F1 TV</t>
         </is>
@@ -4101,14 +5173,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 management commentary on the Liberty Media Q2 2026 earnings call (ex-US F1 TV revenue +18% YTD); base from FY2025 10-K Note 7.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (DTC) — other digital</t>
         </is>
@@ -4123,14 +5195,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7, other digital media rights $18.589m.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -4145,14 +5217,14 @@
           <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple Newsroom, 17 Oct 2025 (no fee). Fee band: CNBC; Sports Business Journal/Puck; BBC ($750m over five years).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -4168,14 +5240,14 @@
 https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Sky, 6 May 2026 (term, no fee). Fee: SportsPro, £645m over seven years, cross-checked against the BlackBook F1 Business Report.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -4191,14 +5263,14 @@
 https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport Bild; GPBlog; WEB.DE, €50-55m a year. Multi-bidder 2028 tender: F1 management comments to Motorsport-Magazin, July 2026; DigitalFernsehen.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL</t>
         </is>
@@ -4213,14 +5285,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">DWDL, RTL and Sky sublicence arrangement.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -4235,14 +5307,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF ~€15m rights + ~€5m production for half-calendar sublicence; derStandard industry estimate &gt;€15m a year.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ORF</t>
         </is>
@@ -4257,14 +5329,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF rights and production cost for the half-calendar sublicence.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -4279,14 +5351,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR service announcements; F1 broadcaster directory. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -4301,14 +5373,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Équipe, April 2022: &gt;€60m a year for France plus Francophone Africa.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -4323,14 +5395,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Équipe and RMC, Canal+ (Maxime Saada) on a significant increase. No figure published.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -4345,14 +5417,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and DAZN, 8 Sep 2026 (term). Fee: 2Playbook, Spain €40-50m; prior Telefónica face ~€45m.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -4367,14 +5439,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, NL plus Nordics package ~$47m a year; NOS, Telegraaf and TotaalTV on the Dutch €45m component.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -4389,14 +5461,14 @@
           <t xml:space="preserve">https://grupapolsatplus.pl/en/archive/formula-1-back-eleven-sports-network-has-secured-exclusive-rights-next-four-seasons</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Cyfrowy Polsat, 30 Oct 2024: exclusive 2025-28, record fee, no figure. Prior cycle ~$15m per GlobalData/Sportcal.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -4411,14 +5483,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Magyar Hang, prior package $43.39m over 2023-25; MTI, December 2025 renewal through 2027.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -4433,14 +5505,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nova Sport launch announcements; F1 broadcaster directory. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -4455,14 +5527,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Infront, Balkans sublicence June 2025; F1 broadcaster directory for the constituent territories. All fees unpublished.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -4477,14 +5549,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and ESPN, February 2026 (term, no fee). Prior cycle: SportsBusiness Journal on Mediapro, 2014.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -4499,14 +5571,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Globo, 11 Jul 2025 (term, no fee); fee ~$8m a year reported by UOL.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Band</t>
         </is>
@@ -4521,14 +5593,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Folha de S.Paulo, Band ~$15m a year.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -4543,14 +5615,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports Mexico exit, ~$1.5m for six races; Televisa/Sky Mexico renewal reported late 2025, fee undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -4565,14 +5637,14 @@
           <t xml:space="preserve">https://corp.formula1.com/formula-1-and-bell-medias-tsn-and-rds-announce-multi-year-media-rights-extension-for-canada/</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Bell Media, 2 Mar 2020: multi-year extension (term only, no fee). Canadian GP hosting agreement to 2035 reported by SportsBusiness Journal.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -4587,14 +5659,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Bloomberg and Reuters, November 2023: &gt;$500m over ten years.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -4609,14 +5681,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and beIN, February 2026 (term, no fee); Liberty Media Q1 2026 commentary on the pan-Asia extension.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -4631,14 +5703,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">SportBusiness, 2020: SuperSport fee steady. MultiChoice annual report, no F1 isolate.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -4653,14 +5725,14 @@
           <t xml:space="preserve">https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Fuji TV, 4 Dec 2025 (term, no fee); Sponichi, tens-of-billions-of-yen scale.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -4675,14 +5747,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Tencent renewal, term through 2027 (no fee); Lanxiong Sports on historic Chinese right values.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -4697,14 +5769,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and FanCode, December 2025 (term, no fee); SportBusiness on digital-only market value.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -4719,14 +5791,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play extension, September 2025; ELTA Chinese Taipei through 2029. Fees unpublished.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -4741,14 +5813,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sydney Morning Herald, A$45m a year for the incumbents.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Kayo Sports / Foxtel</t>
         </is>
@@ -4763,14 +5835,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1, Kayo and Foxtel new deal announced 2026; Sydney Morning Herald, A$60m a year from 2027.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -4785,14 +5857,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky New Zealand, September 2025 three-year renewal (no fee); Coliseum history ~$1.5m a year.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -4807,14 +5879,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">VOV, TV360 exclusive 2026-28. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -4829,14 +5901,14 @@
           <t xml:space="preserve">https://corp.formula1.com/</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 broadcaster directory, in-ship and in-flight listing. Fee unpublished.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 (pooled residual) — F2/F3, archive, radio, ancillary</t>
         </is>
@@ -4851,14 +5923,14 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A and Revenue Recognition note: media rights fees from F1 Event broadcast, F2 and F3 races, F1 TV subscriptions, origination and archive footage, radio and other ancillary media rights.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 movie (Brad Pitt)</t>
         </is>
@@ -4873,29 +5945,29 @@
           <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A: one-time revenue associated with the release of the F1 movie.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sports Business Journal, June 2023: ESPN ~$87.5m a year.</t>
         </is>
@@ -4913,120 +5985,120 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">Item</t>
         </is>
       </c>
-      <c r="B1" s="63" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis convention</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">HARD = disclosed in a filing or by a party. TRADE = figure reported in trade or business press, parties silent. EST = modelled where no figure is published. ASSUMP = reconciliation residual.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Reported anchor</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K reports Formula 1 media rights revenue of $1,212.25m. That is the only total anchor; 2026-28 have no reported comparator.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Residual construction</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Pooled residual = $1,212.25m minus every other included row for 2025, held flat in dollars thereafter. Not escalated, so forward growth comes only from named deals.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Term column</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start and Term End hold four-digit years only. 'OPEN' means the term end has not been announced or is open-ended. Both columns are stored as text so a year is never reformatted.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">US step-up</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple at $131.5m in 2026 against ESPN at $87.5m in 2025 is a $44m, ~50% increase, the largest single-deal uplift in the book.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Term corrections vs source file</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky UK and Ireland now run to 2034 and Sky Italia to 2032 (both announced 6 May 2026). Apple and Globo both start in 2026, not 2025. Band ended with 2025.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Platform data</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Platform descriptions reflect the announced package per territory where a primary announcement was reviewed; otherwise the source file's package_type.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Excluded rows</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL, ORF and Network 10 are sublicences or free-to-air windows paid to the primary rights holder, not to F1; including them would double count. ESPN (to 2025), Band (to 2025) and the F1 movie are one-off or expired and sit outside the forward run rate.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Known weak points</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada media (bundled with GP hosting), Japan, Korea/SEA basket and Switzerland carry the widest ranges. Apple is the largest single forecast risk.</t>
         </is>
@@ -5047,26 +6119,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Line</t>
         </is>
       </c>
-      <c r="B1" s="61">
+      <c r="B1" s="62">
         <v>2025</v>
       </c>
-      <c r="C1" s="61">
+      <c r="C1" s="62">
         <v>2026</v>
       </c>
-      <c r="D1" s="61">
+      <c r="D1" s="62">
         <v>2027</v>
       </c>
-      <c r="E1" s="54">
+      <c r="E1" s="55">
         <v>2028</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Named territory, DTC and designated-territory deals</t>
         </is>
@@ -5080,12 +6152,12 @@
       <c r="D2" s="6">
         <v>1032.59</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>1066.03</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Pooled residual (F2/F3, archive, radio, ancillary)</t>
         </is>
@@ -5099,12 +6171,12 @@
       <c r="D3" s="6">
         <v>421.85</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>421.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Total modelled media revenue</t>
         </is>
@@ -5118,12 +6190,12 @@
       <c r="D4" s="6">
         <v>1454.44</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>1487.88</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty reported FY2025 media rights revenue</t>
         </is>
@@ -5137,26 +6209,26 @@
       <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Variance vs reported</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>0</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5184,79 +6256,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Media Rights Holder</t>
         </is>
       </c>
-      <c r="C1" s="70" t="inlineStr">
+      <c r="C1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Platforms / Broadcast Rights</t>
         </is>
       </c>
-      <c r="D1" s="88" t="inlineStr">
+      <c r="D1" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">Term Start</t>
         </is>
       </c>
-      <c r="E1" s="88" t="inlineStr">
+      <c r="E1" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">Term End</t>
         </is>
       </c>
-      <c r="F1" s="88" t="inlineStr">
+      <c r="F1" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="G1" s="313" t="inlineStr">
+      <c r="G1" s="314" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2025 (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="313" t="inlineStr">
+      <c r="H1" s="314" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2026 (USD m)</t>
         </is>
       </c>
-      <c r="I1" s="313" t="inlineStr">
+      <c r="I1" s="314" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2027 (USD m)</t>
         </is>
       </c>
-      <c r="J1" s="313" t="inlineStr">
+      <c r="J1" s="314" t="inlineStr">
         <is>
           <t xml:space="preserve">Est. Revenue 2028 (USD m)</t>
         </is>
       </c>
-      <c r="K1" s="88" t="inlineStr">
+      <c r="K1" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">In Total</t>
         </is>
       </c>
-      <c r="L1" s="70" t="inlineStr">
+      <c r="L1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
-      <c r="M1" s="70" t="inlineStr">
+      <c r="M1" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyst Notes</t>
         </is>
       </c>
-      <c r="N1" s="63" t="inlineStr">
+      <c r="N1" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">Sources</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Global ex-US</t>
         </is>
@@ -5311,7 +6383,7 @@
           <t xml:space="preserve">The only audited, partner-level line in the stack: Liberty's FY2025 10-K puts subscription-based services at $181.797m. Source workbook carries a separate DTC_GROWTH row (+$32.7m, +18% ex-US YTD per the Q2 2026 call); it is a disclosed overlay on this same fee, so merging it prevents a double count. The FY2025 base is held flat and the 18% is treated as upside, because the US leaves this line in 2026.</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7 (Formula One Digital Media Ltd, subscription-based services $181.797m). Growth: Liberty Media Q2 2026 earnings call, ex-US F1 TV revenue +18% YTD.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm
@@ -5320,7 +6392,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -5375,7 +6447,7 @@
           <t xml:space="preserve">Second disclosed line from the FY2025 10-K ($18.589m), event-contracted. Held flat for lack of growth disclosure; at under 2% of the total the flat carry is immaterial.</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, Note 7, other digital media rights $18.589m.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -5383,7 +6455,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
@@ -5436,7 +6508,7 @@
           <t xml:space="preserve">$145m is the midpoint of the $140m (CNBC, SBJ/Puck) to $150m (BBC) trade band, reached on a 5% step from a $131.5m 2026 start so the package totals roughly $750m. Largest single forecast risk in the book: a $10m error moves the total by about 1%. Against ESPN's $87.5m the US fee rises roughly 50%.</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple Newsroom, 17 Oct 2025 (term, no fee). Fee band: CNBC; Sports Business Journal/Puck; BBC ($750m over five years).
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
@@ -5444,7 +6516,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
         </is>
@@ -5497,7 +6569,7 @@
           <t xml:space="preserve">The one disclosed prior cycle (Mediapro, 2015-19) ran at about EUR20m+ a year, a floor well below the $35m carried here; the premium reflects DTS-era regional repricing. No trade print exists for the 2026-28 cycle, so the number is directional.</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and ESPN, February 2026 (term, no fee). Prior cycle: Sports Business Journal on Mediapro, 2014.
 https://corp.formula1.com/</t>
@@ -5505,7 +6577,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Brazil</t>
         </is>
@@ -5558,7 +6630,7 @@
           <t xml:space="preserve">About $8m a year, below the $15m Band paid and below the $13m Record reportedly bid; Globo traded fee for reach. Brazil is the one large market where the renewal went down rather than up. The source workbook escalates from a $7.69m 2026 start, so the $8m trade figure lands in 2027.</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Globo, 11 Jul 2025 (term, no fee); fee ~$8m a year reported by UOL.
 https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
@@ -5566,7 +6638,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mexico</t>
         </is>
@@ -5619,7 +6691,7 @@
           <t xml:space="preserve">Fox Sports paid about $1.5m for the last six races of 2025, a distressed exit that annualises to roughly $6m and sets a floor; Televisa repriced upward late in 2025. $8m sits above that floor. No published fee for the Televisa cycle.</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports Mexico exit, ~$1.5m for six races; Televisa/Sky Mexico renewal reported late 2025, fee undisclosed.
 https://corp.formula1.com/</t>
@@ -5627,7 +6699,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada</t>
         </is>
@@ -5680,7 +6752,7 @@
           <t xml:space="preserve">Rights are bundled with Canadian GP hosting and neither Bell nor F1 disclosed a media fee. The estimate is an $8-10m cable package escalated to about $12m by end of term. Boundary that matters: the separate ~$18.7m GP hosting fee sits on the race-promotion calendar and must not be added here.</t>
         </is>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Bell Media, 2 Mar 2020: multi-year extension (term only, no fee). Canadian GP hosting agreement to 2035 reported by Sports Business Journal.
 https://corp.formula1.com/formula-1-and-bell-medias-tsn-and-rds-announce-multi-year-media-rights-extension-for-canada/</t>
@@ -5688,7 +6760,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">United Kingdom, Ireland &amp; Italy</t>
         </is>
@@ -5741,7 +6813,7 @@
           <t xml:space="preserve">Neither party disclosed a fee; GBP645m over seven years (SportsPro/BlackBook) gives about $117m for the combined three-territory package at the 2025 level, escalated 3%. Two source rows are merged here: the 2023-29 package and the 2030-34 forward at $255m, which is not bookable because the current cycle still governs through 2029.</t>
         </is>
       </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Sky, 6 May 2026 (term, no fee). Fee: SportsPro, GBP645m over seven years, cross-checked against the BlackBook F1 Business Report.
 https://corp.formula1.com/formula-1-and-sky-agree-long-term-partnership-across-uk-ireland-and-italy/
@@ -5750,7 +6822,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Germany</t>
         </is>
@@ -5803,7 +6875,7 @@
           <t xml:space="preserve">EUR50-55m band reported by Sport Bild, GPBlog and WEB.DE, taken at $55m and escalated 4%. Germany is the most likely territory for a step change under new RTL ownership. That upside stays in this note rather than in the numbers, because booking a tender placeholder would put $75m into 2028 the parties have not agreed.</t>
         </is>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport Bild; GPBlog; WEB.DE, EUR50-55m a year. 2028 tender: F1 management to Motorsport-Magazin, July 2026; DigitalFernsehen. RTL sublicence: DWDL.
 https://corp.formula1.com/</t>
@@ -5811,7 +6883,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Austria</t>
         </is>
@@ -5864,7 +6936,7 @@
           <t xml:space="preserve">F1 has not published the fee. $18m is anchored off the disclosed ORF sublicence: oe24 reported ORF paying about EUR15m in rights plus EUR5m production for a half-calendar package, which sets a floor for the master deal ServusTV buys. derStandard's industry estimate above EUR15m a year corroborates. The ORF row in the source file is a reallocation of the same money, not an addition.</t>
         </is>
       </c>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">oe24, ORF ~EUR15m rights + ~EUR5m production for half-calendar sublicence; derStandard industry estimate &gt;EUR15m a year.
 https://corp.formula1.com/</t>
@@ -5872,7 +6944,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Switzerland</t>
         </is>
@@ -5927,7 +6999,7 @@
           <t xml:space="preserve">No disclosed figure in any Swiss public filing reviewed. $8m is a population-based haircut on the Austrian estimate, allowing for Switzerland's higher rights value per capita, and escalates 4%. Low confidence but small: a 50% error moves the total by about 0.3%.</t>
         </is>
       </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR service announcements; F1 broadcaster directory. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -5935,7 +7007,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Belgium</t>
         </is>
@@ -5988,7 +7060,7 @@
           <t xml:space="preserve">No published fee in any Belgian source reviewed. $9m is an EST on a small-Euro peer basis, below the Czech and Hungarian rows despite the larger F1 footprint because Belgian rights are split free-to-air and pay. Low confidence, small weight.</t>
         </is>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, RTBF extension through 2027; Telenet Play Sports renewal. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -5996,7 +7068,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
         </is>
@@ -6049,7 +7121,7 @@
           <t xml:space="preserve">One row, two components merged: $63.7m is the EUR60m reported floor at about 1.08, and $19.6m is the incremental value implied by Canal+ describing the renewal as a significant increase, taken at the low end of a 25-50% uplift band. The source workbook carries those as two rows; merging them stops the uplift being read as a separate contract. A EUR90m reading circulating on an unverified student blog was rejected. Francophone Africa is inside this fee, so no separate Canal+ Afrique row exists.</t>
         </is>
       </c>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">L'Equipe, April 2022: &gt;EUR60m a year for France plus Francophone Africa. RMC, Canal+ (Maxime Saada) on a significant increase. No combined figure published.
 https://corp.formula1.com/</t>
@@ -6057,7 +7129,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
         </is>
@@ -6110,7 +7182,7 @@
           <t xml:space="preserve">Split at about $60m Spain plus $7m Portugal, escalated 4%. Deliberately above the EUR45m Telefonica reference and the EUR40-50m Spanish band because DAZN took exclusivity and added Portugal. A buy-side note puts combined Spain, Germany and Italy at about $250m against roughly $183m booked across those rows; the rows were not re-based to close that gap, and the source file's $192m proxy row is excluded for the same reason.</t>
         </is>
       </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and DAZN, 8 Sep 2026 (term). Fee: 2Playbook, Spain EUR40-50m; prior Telefonica face ~EUR45m.
 https://corp.formula1.com/</t>
@@ -6118,7 +7190,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Netherlands &amp; Nordics</t>
         </is>
@@ -6171,7 +7243,7 @@
           <t xml:space="preserve">Sportcal reported the combined package at about $47m a year, so $49m sits just inside that print, with the Netherlands driving most of it. Escalated 4%. The step from roughly $30m for the Netherlands alone is one of the steeper renewal uplifts in the book.</t>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
+      <c r="N16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal, NL plus Nordics package ~$47m a year; NOS, Telegraaf and TotaalTV on the Dutch EUR45m component.
 https://corp.formula1.com/</t>
@@ -6179,7 +7251,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Poland</t>
         </is>
@@ -6232,7 +7304,7 @@
           <t xml:space="preserve">Cyfrowy Polsat's announcement described a record fee without a number, so $17m is the prior Viaplay cycle (about $15m per GlobalData) plus an uplift for the record-fee language. Direction of travel is reliable, magnitude is not.</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Cyfrowy Polsat, 30 Oct 2024: exclusive 2025-28, record fee, no figure. Prior cycle ~$15m per GlobalData/Sportcal.
 https://grupapolsatplus.pl/en/archive/formula-1-back-eleven-sports-network-has-secured-exclusive-rights-next-four-seasons</t>
@@ -6240,7 +7312,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Hungary</t>
         </is>
@@ -6293,7 +7365,7 @@
           <t xml:space="preserve">$14.5m a year derives from the reported $43.39m three-year prior package, escalated 4%; the 2026-27 renewal fee is undisclosed. MTVA pays through Hungaroring Sport, the race promoter, so the amount reaching F1 is at or below this face value.</t>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Magyar Hang, prior package $43.39m over 2023-25; MTI, December 2025 renewal through 2027.
 https://corp.formula1.com/</t>
@@ -6301,7 +7373,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Czechia &amp; Slovakia</t>
         </is>
@@ -6354,7 +7426,7 @@
           <t xml:space="preserve">No published fee in either cycle. $6m is a population and GDP haircut on the Polish and Hungarian rows, escalated 4%. A 50% error moves the total by 0.2%.</t>
         </is>
       </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="N19" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nova Sport launch announcements; F1 broadcaster directory. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -6362,7 +7434,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Rest of Europe &amp; Israel</t>
         </is>
@@ -6417,7 +7489,7 @@
           <t xml:space="preserve">Long-tail basket carried at about $11m, built bottom-up at roughly EUR0.3-1.5m per market. Every constituent fee is unpublished. The Infront Balkans sublicence signed in June 2025 is the largest single piece.</t>
         </is>
       </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Infront, Balkans sublicence June 2025; F1 broadcaster directory for the constituent territories. All fees unpublished.
 https://corp.formula1.com/</t>
@@ -6425,7 +7497,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
         </is>
@@ -6478,7 +7550,7 @@
           <t xml:space="preserve">$50m a year is the $500m-plus ten-year print divided down, escalated 4%, so early years sit below the term average. It is a face-value figure that may be gross of production or marketing commitments in a way the European rows are not, which is why it is not treated as directly comparable.</t>
         </is>
       </c>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="N21" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Bloomberg and Reuters, November 2023: &gt;$500m over ten years.
 https://corp.formula1.com/</t>
@@ -6486,7 +7558,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia (10 territories) — beIN</t>
         </is>
@@ -6539,7 +7611,7 @@
           <t xml:space="preserve">Set at roughly 0.3-0.8x the MENA value, scaled down for a far lower per-capita rights market. beIN's own release cites double-digit audience growth in the region, supporting a renewal at or above the prior fee. No trade print for either cycle. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="N22" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and beIN, February 2026 (term, no fee); Liberty Media Q1 2026 commentary on the pan-Asia extension.
 https://corp.formula1.com/</t>
@@ -6547,7 +7619,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sub-Saharan Africa</t>
         </is>
@@ -6602,7 +7674,7 @@
           <t xml:space="preserve">MultiChoice's annual report does not isolate an F1 line and SportBusiness reported the fee as broadly steady in 2020, so $10m is directional. The continent is split by language: this row covers English-speaking Africa, Canal+ covers Francophone Africa, with no overlap.</t>
         </is>
       </c>
-      <c r="N23" s="14" t="inlineStr">
+      <c r="N23" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">SportBusiness, 2020: SuperSport fee steady. MultiChoice annual report, no F1 isolate.
 https://corp.formula1.com/</t>
@@ -6610,7 +7682,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Japan</t>
         </is>
@@ -6663,7 +7735,7 @@
           <t xml:space="preserve">F1's December 2025 announcement disclosed the term but not the fee. Sponichi's 'several-billion-yen' report brackets roughly $13-60m; $22m sits toward the top because the package is exclusive across all rights rather than split between pay and free-to-air as under DAZN. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N24" s="14" t="inlineStr">
+      <c r="N24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Fuji TV, 4 Dec 2025 (term, no fee); Sponichi, tens-of-billions-of-yen scale.
 https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
@@ -6671,7 +7743,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">China</t>
         </is>
@@ -6724,7 +7796,7 @@
           <t xml:space="preserve">Chinese rights have been priced very low historically: Tencent's prior bid was reported around $0.5m a year and a China Telecom non-exclusive deal around $1m. $5m assumes the exclusive digital-plus-free-to-air stack repriced well above that micro floor. A $110m figure circulating on a rights blog was rejected as inconsistent with every audit trail in the market.</t>
         </is>
       </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="N25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and Tencent renewal, term through 2027 (no fee); Lanxiong Sports on historic Chinese right values.
 https://corp.formula1.com/</t>
@@ -6732,7 +7804,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">India, Bangladesh, Nepal &amp; Sri Lanka</t>
         </is>
@@ -6785,7 +7857,7 @@
           <t xml:space="preserve">FanCode sells a season pass at INR599, which caps what the market bears. No fee published in either cycle and SportBusiness characterised the deal as market value for digital-only rights, so $5m is directional and low confidence.</t>
         </is>
       </c>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="N26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 and FanCode, December 2025 (term, no fee); SportBusiness on digital-only market value.
 https://corp.formula1.com/</t>
@@ -6793,7 +7865,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Korea, Chinese Taipei &amp; residual SE Asia</t>
         </is>
@@ -6846,7 +7918,7 @@
           <t xml:space="preserve">No value published for any deal in this basket, so $4.5m is a residual sized between the Indian and Vietnamese rows. The least-supported line in the book and the first candidate for revision if any single fee surfaces.</t>
         </is>
       </c>
-      <c r="N27" s="14" t="inlineStr">
+      <c r="N27" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play extension, September 2025; ELTA Chinese Taipei through 2029. Fees unpublished.
 https://corp.formula1.com/</t>
@@ -6854,7 +7926,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Australia</t>
         </is>
@@ -6907,7 +7979,7 @@
           <t xml:space="preserve">A$45m escalated 4% gives $31.2m for 2025 and $32.45m for 2026; the new deal converts A$60m at about 0.70 to $42m in 2027, escalated 4%. The source workbook splits this into two rows and books the new deal only in 2028; merging them avoids a gap year and a duplicate. Unlike most rows the 2027 step is a trade print on an actual contracted value rather than an estimate of an undisclosed sum.</t>
         </is>
       </c>
-      <c r="N28" s="14" t="inlineStr">
+      <c r="N28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sydney Morning Herald, A$45m a year for the incumbents; Formula 1, Kayo and Foxtel new deal announced 2026, A$60m a year from 2027.
 https://corp.formula1.com/</t>
@@ -6915,7 +7987,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">New Zealand</t>
         </is>
@@ -6968,7 +8040,7 @@
           <t xml:space="preserve">Prior history is about $1.5m a year. $3m reflects the Lawson-era uplift in New Zealand interest plus 4% escalation. No published fee in either cycle. Carried from 2025 because the predecessor package overlapped the year.</t>
         </is>
       </c>
-      <c r="N29" s="14" t="inlineStr">
+      <c r="N29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky New Zealand, September 2025 three-year renewal (no fee); Coliseum history ~$1.5m a year.
 https://corp.formula1.com/</t>
@@ -6976,7 +8048,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Vietnam</t>
         </is>
@@ -7029,7 +8101,7 @@
           <t xml:space="preserve">New market entry with no published fee and no predecessor to anchor on. $2m is a floor estimate for a single-country streaming deal, with wide error bars.</t>
         </is>
       </c>
-      <c r="N30" s="14" t="inlineStr">
+      <c r="N30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">VOV, TV360 exclusive 2026-28. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -7037,7 +8109,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Global in-flight and in-ship</t>
         </is>
@@ -7092,7 +8164,7 @@
           <t xml:space="preserve">Micro deal with no published value, sized at $1.5m against the New Zealand and Vietnam rows. Immaterial to the total but included so the territory list matches F1's own broadcaster directory.</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="N31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 broadcaster directory, in-ship and in-flight listing. Fee unpublished.
 https://corp.formula1.com/</t>
@@ -7100,7 +8172,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -7155,7 +8227,7 @@
           <t xml:space="preserve">This is the arithmetic gap that makes the named rows tie to the reported total, not a partner fee. 2025 is Liberty's reported $1,212.25m minus every other included row, held flat in dollars thereafter. Flat rather than escalated on purpose: escalating a residual this large would manufacture roughly $15m a year of revenue F1 has not guided to. Forward growth in the book therefore comes only from named deals. Read it as a reconciliation line, not a contract.</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr">
+      <c r="N32" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A and revenue note: media rights fees from licensing broadcast of F1 Events and F2/F3 races, F1 TV subscriptions, origination and archive footage, radio and other ancillary media rights.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -7163,7 +8235,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT IN TOTAL (expired or one-off)</t>
         </is>
@@ -7188,10 +8260,10 @@
       <c r="K33" s="33"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
-      <c r="N33" s="14"/>
+      <c r="N33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
@@ -7244,7 +8316,7 @@
           <t xml:space="preserve">Retained so the 2025 mix is visible: Apple's $131.5m against ESPN's $87.5m is roughly a 50% increase, the largest single-deal uplift in the period. Excluded from every total.</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
+      <c r="N34" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Sports Business Journal, June 2023: ESPN ~$87.5m a year.
 https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
@@ -7252,7 +8324,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Brazil</t>
         </is>
@@ -7305,7 +8377,7 @@
           <t xml:space="preserve">Carried for continuity only. Folha's $15m print is the reference that shows how far Globo's fee fell.</t>
         </is>
       </c>
-      <c r="N35" s="14" t="inlineStr">
+      <c r="N35" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Folha de S.Paulo, Band ~$15m a year.
 https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
@@ -7313,7 +8385,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
@@ -7366,7 +8438,7 @@
           <t xml:space="preserve">Liberty's FY2025 MD&amp;A cites one-time revenue from the film release in explaining media rights growth. Booked at $15m in 2025 only; including it would overstate the 2026 base.</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Liberty Media FY2025 10-K, MD&amp;A: one-time revenue associated with the release of the F1 movie.
 https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm</t>
@@ -7374,32 +8446,32 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">RECONCILED TOTAL (included rows)</t>
         </is>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <v>1212.25</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="16">
         <v>1418.76</v>
       </c>
-      <c r="D37" s="35">
+      <c r="D37" s="34">
         <v>1459.1</v>
       </c>
-      <c r="E37" s="35">
+      <c r="E37" s="34">
         <v>1477.09</v>
       </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="260"/>
-      <c r="H37" s="260"/>
-      <c r="I37" s="260"/>
-      <c r="J37" s="260"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="11"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="259"/>
+      <c r="H37" s="259"/>
+      <c r="I37" s="259"/>
+      <c r="J37" s="259"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="12"/>
     </row>
   </sheetData>
 </worksheet>
@@ -7425,79 +8497,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t xml:space="preserve">Media Rights Holder</t>
         </is>
       </c>
-      <c r="B1" s="106" t="inlineStr">
+      <c r="B1" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="61" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Term</t>
         </is>
       </c>
-      <c r="D1" s="61" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="E1" s="61" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">In Total</t>
         </is>
       </c>
-      <c r="F1" s="61" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Change Type</t>
         </is>
       </c>
-      <c r="G1" s="493" t="inlineStr">
+      <c r="G1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">2025 (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="493" t="inlineStr">
+      <c r="H1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 (USD m)</t>
         </is>
       </c>
-      <c r="I1" s="601" t="inlineStr">
+      <c r="I1" s="602" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta (USD m)</t>
         </is>
       </c>
-      <c r="J1" s="709" t="inlineStr">
+      <c r="J1" s="710" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta %</t>
         </is>
       </c>
-      <c r="K1" s="61" t="inlineStr">
+      <c r="K1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Modelled?</t>
         </is>
       </c>
-      <c r="L1" s="493" t="inlineStr">
+      <c r="L1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">Range low (USD m)</t>
         </is>
       </c>
-      <c r="M1" s="493" t="inlineStr">
+      <c r="M1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">Range high (USD m)</t>
         </is>
       </c>
-      <c r="N1" s="99" t="inlineStr">
+      <c r="N1" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">What's changing</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— STEP-UP —</t>
         </is>
@@ -7514,10 +8586,10 @@
       <c r="K2" s="6"/>
       <c r="L2" s="438"/>
       <c r="M2" s="438"/>
-      <c r="N2" s="50"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney (prior cycle)</t>
         </is>
@@ -7567,7 +8639,7 @@
       <c r="L3" s="438"/>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Band</t>
         </is>
@@ -7617,7 +8689,7 @@
       <c r="L4" s="438"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 movie (Brad Pitt)</t>
         </is>
@@ -7667,7 +8739,7 @@
       <c r="L5" s="438"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -7717,7 +8789,7 @@
       <c r="L6" s="438"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Step-up</t>
         </is>
@@ -7739,7 +8811,7 @@
       <c r="J7" s="654"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— NEW DEAL —</t>
         </is>
@@ -7756,10 +8828,10 @@
       <c r="K8" s="6"/>
       <c r="L8" s="438"/>
       <c r="M8" s="438"/>
-      <c r="N8" s="50"/>
+      <c r="N8" s="49"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -7811,7 +8883,7 @@
       <c r="L9" s="438"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -7866,14 +8938,14 @@
       <c r="M10" s="438">
         <v>45</v>
       </c>
-      <c r="N10" s="50" t="inlineStr">
+      <c r="N10" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">First year of the 2026-28 LatAm/Caribbean cycle inside the wider Disney agreement. Estimated: the previous cycle was not split out, so no prior-year figure exists.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -7925,7 +8997,7 @@
       <c r="L11" s="438"/>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -7980,14 +9052,14 @@
       <c r="M12" s="438">
         <v>2.5</v>
       </c>
-      <c r="N12" s="50" t="inlineStr">
+      <c r="N12" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">New Vietnam entry from 2026. Estimated: no public fee; sized at $2m as a small-population first cycle.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -8042,14 +9114,14 @@
       <c r="M13" s="438">
         <v>25</v>
       </c>
-      <c r="N13" s="50" t="inlineStr">
+      <c r="N13" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Exclusive Japanese deal 2026-30 replacing the prior shared arrangement. Estimated at ~$20m a year, consistent with Japan sitting just below the beIN Asia package.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -8104,14 +9176,14 @@
       <c r="M14" s="438">
         <v>6</v>
       </c>
-      <c r="N14" s="50" t="inlineStr">
+      <c r="N14" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Korea, Chinese Taipei and residual South-East Asia re-contracted from 2026 as one package. Estimated at ~$4.5m a year.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -8166,14 +9238,14 @@
       <c r="M15" s="438">
         <v>4</v>
       </c>
-      <c r="N15" s="50" t="inlineStr">
+      <c r="N15" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">New Zealand renews for 2026-28. Estimated at ~$3m a year for a two-island market.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">New deal</t>
         </is>
@@ -8195,7 +9267,7 @@
       <c r="J16" s="654"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— ESCALATOR —</t>
         </is>
@@ -8212,10 +9284,10 @@
       <c r="K17" s="6"/>
       <c r="L17" s="438"/>
       <c r="M17" s="438"/>
-      <c r="N17" s="50"/>
+      <c r="N17" s="49"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -8265,7 +9337,7 @@
       <c r="L18" s="438"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -8315,7 +9387,7 @@
       <c r="L19" s="438"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -8365,7 +9437,7 @@
       <c r="L20" s="438"/>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -8415,7 +9487,7 @@
       <c r="L21" s="438"/>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -8465,7 +9537,7 @@
       <c r="L22" s="438"/>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -8515,7 +9587,7 @@
       <c r="L23" s="438"/>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -8565,7 +9637,7 @@
       <c r="L24" s="438"/>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -8615,7 +9687,7 @@
       <c r="L25" s="438"/>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -8665,7 +9737,7 @@
       <c r="L26" s="438"/>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -8715,7 +9787,7 @@
       <c r="L27" s="438"/>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -8765,7 +9837,7 @@
       <c r="L28" s="438"/>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -8815,7 +9887,7 @@
       <c r="L29" s="438"/>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -8865,7 +9937,7 @@
       <c r="L30" s="438"/>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -8915,7 +9987,7 @@
       <c r="L31" s="438"/>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -8965,7 +10037,7 @@
       <c r="L32" s="438"/>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -9015,7 +10087,7 @@
       <c r="L33" s="438"/>
     </row>
     <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -9065,7 +10137,7 @@
       <c r="L34" s="438"/>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -9115,7 +10187,7 @@
       <c r="L35" s="438"/>
     </row>
     <row r="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -9165,7 +10237,7 @@
       <c r="L36" s="438"/>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Escalator</t>
         </is>
@@ -9187,7 +10259,7 @@
       <c r="J37" s="654"/>
     </row>
     <row r="38">
-      <c r="A38" s="48"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="51"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -9200,10 +10272,10 @@
       <c r="K38" s="6"/>
       <c r="L38" s="438"/>
       <c r="M38" s="438"/>
-      <c r="N38" s="50"/>
+      <c r="N38" s="49"/>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">READ ACROSS</t>
         </is>
@@ -9216,7 +10288,7 @@
       <c r="C39" s="6"/>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">BOOK LEDGER</t>
         </is>
@@ -9229,42 +10301,42 @@
       <c r="C40" s="6">
         <v>1212.25</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="D40" s="6">
+        <v>1411.11</v>
+      </c>
+      <c r="E40" s="6">
+        <v>198.86</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.164</v>
+      </c>
       <c r="G40" s="438"/>
-      <c r="H40" s="438">
-        <v>1411.11</v>
-      </c>
-      <c r="I40" s="546">
-        <v>198.86</v>
-      </c>
-      <c r="J40" s="654">
-        <v>0.164</v>
-      </c>
+      <c r="H40" s="438"/>
+      <c r="I40" s="546"/>
+      <c r="J40" s="654"/>
       <c r="K40" s="6"/>
     </row>
     <row r="41">
-      <c r="A41" s="46" t="inlineStr">
+      <c r="A41" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">Total of listed rows</t>
         </is>
       </c>
-      <c r="B41" s="53" t="inlineStr">
+      <c r="B41" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">30 rows</t>
         </is>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="7">
         <v>81.36</v>
       </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="440"/>
-      <c r="H41" s="440"/>
-      <c r="I41" s="548"/>
-      <c r="J41" s="656"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="439"/>
+      <c r="H41" s="439"/>
+      <c r="I41" s="547"/>
+      <c r="J41" s="655"/>
     </row>
   </sheetData>
 </worksheet>
@@ -9290,79 +10362,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t xml:space="preserve">Media Rights Holder</t>
         </is>
       </c>
-      <c r="B1" s="106" t="inlineStr">
+      <c r="B1" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="C1" s="61" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Term</t>
         </is>
       </c>
-      <c r="D1" s="61" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Basis</t>
         </is>
       </c>
-      <c r="E1" s="61" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">In Total</t>
         </is>
       </c>
-      <c r="F1" s="61" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Change Type</t>
         </is>
       </c>
-      <c r="G1" s="493" t="inlineStr">
+      <c r="G1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 (USD m)</t>
         </is>
       </c>
-      <c r="H1" s="493" t="inlineStr">
+      <c r="H1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">2027 (USD m)</t>
         </is>
       </c>
-      <c r="I1" s="601" t="inlineStr">
+      <c r="I1" s="602" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta (USD m)</t>
         </is>
       </c>
-      <c r="J1" s="709" t="inlineStr">
+      <c r="J1" s="710" t="inlineStr">
         <is>
           <t xml:space="preserve">Delta %</t>
         </is>
       </c>
-      <c r="K1" s="61" t="inlineStr">
+      <c r="K1" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">Modelled?</t>
         </is>
       </c>
-      <c r="L1" s="493" t="inlineStr">
+      <c r="L1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">Range low (USD m)</t>
         </is>
       </c>
-      <c r="M1" s="493" t="inlineStr">
+      <c r="M1" s="494" t="inlineStr">
         <is>
           <t xml:space="preserve">Range high (USD m)</t>
         </is>
       </c>
-      <c r="N1" s="99" t="inlineStr">
+      <c r="N1" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">What's changing</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— STEP-UP —</t>
         </is>
@@ -9379,10 +10451,10 @@
       <c r="K2" s="6"/>
       <c r="L2" s="438"/>
       <c r="M2" s="438"/>
-      <c r="N2" s="50"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
         </is>
@@ -9430,15 +10502,9 @@
         </is>
       </c>
       <c r="L3" s="438"/>
-      <c r="M3" s="438"/>
-      <c r="N3" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Second Australian contract begins in 2027: ~A$45m steps to ~A$60m a year, a one-third uplift worth about +$12m.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Step-up</t>
         </is>
@@ -9448,27 +10514,19 @@
           <t xml:space="preserve">1 deal</t>
         </is>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6">
+        <v>12</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="438"/>
       <c r="H4" s="438"/>
-      <c r="I4" s="546">
-        <v>12</v>
-      </c>
+      <c r="I4" s="546"/>
       <c r="J4" s="654"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="438"/>
-      <c r="M4" s="438"/>
-      <c r="N4" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subtotal of the step-up rows above.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— NEW DEAL —</t>
         </is>
@@ -9485,10 +10543,10 @@
       <c r="K5" s="6"/>
       <c r="L5" s="438"/>
       <c r="M5" s="438"/>
-      <c r="N5" s="50"/>
+      <c r="N5" s="49"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Apple</t>
         </is>
@@ -9536,15 +10594,9 @@
         </is>
       </c>
       <c r="L6" s="438"/>
-      <c r="M6" s="438"/>
-      <c r="N6" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Year 2 of the US deal at a 5% annual escalator, to the $145m 2028 level.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuji TV</t>
         </is>
@@ -9597,14 +10649,14 @@
       <c r="M7" s="438">
         <v>25</v>
       </c>
-      <c r="N7" s="50" t="inlineStr">
+      <c r="N7" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Second-year lift in the 2026-30 Japanese deal; escalates above the book rate. Modelled, not contracted in public.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ESPN / Disney</t>
         </is>
@@ -9657,14 +10709,14 @@
       <c r="M8" s="438">
         <v>45</v>
       </c>
-      <c r="N8" s="50" t="inlineStr">
+      <c r="N8" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Contract escalation in year 2 of the LatAm/Caribbean cycle.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Globo</t>
         </is>
@@ -9712,15 +10764,9 @@
         </is>
       </c>
       <c r="L9" s="438"/>
-      <c r="M9" s="438"/>
-      <c r="N9" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation in year 2 of the Brazilian deal.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
         </is>
@@ -9773,14 +10819,14 @@
       <c r="M10" s="438">
         <v>6</v>
       </c>
-      <c r="N10" s="50" t="inlineStr">
+      <c r="N10" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Contract escalation in year 2 of the re-contracted basket.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sport New Zealand</t>
         </is>
@@ -9833,14 +10879,14 @@
       <c r="M11" s="438">
         <v>4</v>
       </c>
-      <c r="N11" s="50" t="inlineStr">
+      <c r="N11" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Contract escalation in year 2 of the New Zealand deal.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TV360 (Viettel)</t>
         </is>
@@ -9893,14 +10939,14 @@
       <c r="M12" s="438">
         <v>2.5</v>
       </c>
-      <c r="N12" s="50" t="inlineStr">
+      <c r="N12" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Contract escalation in year 2 of the Vietnamese deal.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">New deal</t>
         </is>
@@ -9910,27 +10956,19 @@
           <t xml:space="preserve">7 deals</t>
         </is>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="6">
+        <v>10.34</v>
+      </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="438"/>
       <c r="H13" s="438"/>
-      <c r="I13" s="546">
-        <v>10.34</v>
-      </c>
+      <c r="I13" s="546"/>
       <c r="J13" s="654"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="438"/>
-      <c r="M13" s="438"/>
-      <c r="N13" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subtotal of the new deal rows above.</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">— ESCALATOR —</t>
         </is>
@@ -9947,10 +10985,10 @@
       <c r="K14" s="6"/>
       <c r="L14" s="438"/>
       <c r="M14" s="438"/>
-      <c r="N14" s="50"/>
+      <c r="N14" s="49"/>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports</t>
         </is>
@@ -9998,15 +11036,9 @@
         </is>
       </c>
       <c r="L15" s="438"/>
-      <c r="M15" s="438"/>
-      <c r="N15" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3% contract rate, below the 4% book rate.</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Canal+</t>
         </is>
@@ -10054,15 +11086,9 @@
         </is>
       </c>
       <c r="L16" s="438"/>
-      <c r="M16" s="438"/>
-      <c r="N16" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">DAZN</t>
         </is>
@@ -10110,15 +11136,9 @@
         </is>
       </c>
       <c r="L17" s="438"/>
-      <c r="M17" s="438"/>
-      <c r="N17" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
         </is>
@@ -10166,15 +11186,9 @@
         </is>
       </c>
       <c r="L18" s="438"/>
-      <c r="M18" s="438"/>
-      <c r="N18" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation. Final year: Germany goes to a 2028 tender.</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Viaplay</t>
         </is>
@@ -10222,15 +11236,9 @@
         </is>
       </c>
       <c r="L19" s="438"/>
-      <c r="M19" s="438"/>
-      <c r="N19" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -10278,15 +11286,9 @@
         </is>
       </c>
       <c r="L20" s="438"/>
-      <c r="M20" s="438"/>
-      <c r="N20" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">beIN Sports</t>
         </is>
@@ -10334,15 +11336,9 @@
         </is>
       </c>
       <c r="L21" s="438"/>
-      <c r="M21" s="438"/>
-      <c r="N21" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">ServusTV</t>
         </is>
@@ -10390,15 +11386,9 @@
         </is>
       </c>
       <c r="L22" s="438"/>
-      <c r="M22" s="438"/>
-      <c r="N22" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation; free-to-air inventory rises to 13 races a year from 2027.</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Eleven Sports / Polsat</t>
         </is>
@@ -10446,15 +11436,9 @@
         </is>
       </c>
       <c r="L23" s="438"/>
-      <c r="M23" s="438"/>
-      <c r="N23" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
         </is>
@@ -10502,15 +11486,9 @@
         </is>
       </c>
       <c r="L24" s="438"/>
-      <c r="M24" s="438"/>
-      <c r="N24" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation. Final year; nothing is booked for 2028.</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Antena, ANT1, Arena Sport, Omega, Go3, Sport 5</t>
         </is>
@@ -10558,15 +11536,9 @@
         </is>
       </c>
       <c r="L25" s="438"/>
-      <c r="M25" s="438"/>
-      <c r="N25" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SuperSport (MultiChoice / Canal+)</t>
         </is>
@@ -10614,15 +11586,9 @@
         </is>
       </c>
       <c r="L26" s="438"/>
-      <c r="M26" s="438"/>
-      <c r="N26" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TSN / RDS (Bell Media)</t>
         </is>
@@ -10670,15 +11636,9 @@
         </is>
       </c>
       <c r="L27" s="438"/>
-      <c r="M27" s="438"/>
-      <c r="N27" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
         </is>
@@ -10726,15 +11686,9 @@
         </is>
       </c>
       <c r="L28" s="438"/>
-      <c r="M28" s="438"/>
-      <c r="N28" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">SRG SSR</t>
         </is>
@@ -10782,15 +11736,9 @@
         </is>
       </c>
       <c r="L29" s="438"/>
-      <c r="M29" s="438"/>
-      <c r="N29" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">TV Nova / Nova Sport</t>
         </is>
@@ -10838,15 +11786,9 @@
         </is>
       </c>
       <c r="L30" s="438"/>
-      <c r="M30" s="438"/>
-      <c r="N30" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Tencent, Shanghai TV, Guangdong TV</t>
         </is>
@@ -10894,15 +11836,9 @@
         </is>
       </c>
       <c r="L31" s="438"/>
-      <c r="M31" s="438"/>
-      <c r="N31" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation. Final year: China falls to zero in 2028 with no renewal in the file.</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">FanCode</t>
         </is>
@@ -10950,15 +11886,9 @@
         </is>
       </c>
       <c r="L32" s="438"/>
-      <c r="M32" s="438"/>
-      <c r="N32" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Sport 24 / Sport 24 Extra</t>
         </is>
@@ -11006,15 +11936,9 @@
         </is>
       </c>
       <c r="L33" s="438"/>
-      <c r="M33" s="438"/>
-      <c r="N33" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contract escalation.</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Escalator</t>
         </is>
@@ -11024,27 +11948,19 @@
           <t xml:space="preserve">19 deals</t>
         </is>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="6">
+        <v>20.99</v>
+      </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="438"/>
       <c r="H34" s="438"/>
-      <c r="I34" s="546">
-        <v>20.99</v>
-      </c>
+      <c r="I34" s="546"/>
       <c r="J34" s="654"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="438"/>
-      <c r="M34" s="438"/>
-      <c r="N34" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subtotal of the escalator rows above.</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="48"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="51"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -11057,10 +11973,10 @@
       <c r="K35" s="6"/>
       <c r="L35" s="438"/>
       <c r="M35" s="438"/>
-      <c r="N35" s="50"/>
+      <c r="N35" s="49"/>
     </row>
     <row r="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">READ ACROSS</t>
         </is>
@@ -11071,24 +11987,9 @@
         </is>
       </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="438"/>
-      <c r="H36" s="438"/>
-      <c r="I36" s="546"/>
-      <c r="J36" s="654"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="438"/>
-      <c r="M36" s="438"/>
-      <c r="N36" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Step-up +12.00, new deals +10.34, escalators +20.99. 18 of 19 escalator rows move at the 4% book rate; Sky UK at 3% is the exception.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">BOOK LEDGER</t>
         </is>
@@ -11098,60 +11999,1351 @@
           <t xml:space="preserve">Calendar total 2027 less 2026, versus the rows above</t>
         </is>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="438">
+      <c r="C37" s="6">
         <v>1411.11</v>
       </c>
-      <c r="H37" s="438">
+      <c r="D37" s="6">
         <v>1454.44</v>
       </c>
-      <c r="I37" s="546">
+      <c r="E37" s="6">
         <v>43.33</v>
       </c>
-      <c r="J37" s="654">
+      <c r="F37" s="6">
         <v>0.0307</v>
       </c>
+      <c r="G37" s="438"/>
+      <c r="H37" s="438"/>
+      <c r="I37" s="546"/>
+      <c r="J37" s="654"/>
       <c r="K37" s="6"/>
-      <c r="L37" s="438"/>
-      <c r="M37" s="438"/>
-      <c r="N37" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rows above sum to +43.33; the book moves +43.33. Nothing is unaccounted for in 2027.</t>
-        </is>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="46" t="inlineStr">
+      <c r="A38" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">Total of listed rows</t>
         </is>
       </c>
-      <c r="B38" s="53" t="inlineStr">
+      <c r="B38" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">27 rows</t>
         </is>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="440"/>
-      <c r="H38" s="440"/>
-      <c r="I38" s="548">
+      <c r="C38" s="7">
         <v>43.33</v>
       </c>
-      <c r="J38" s="656"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="440"/>
-      <c r="M38" s="440"/>
-      <c r="N38" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In-total movements only.</t>
-        </is>
-      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="439"/>
+      <c r="H38" s="439"/>
+      <c r="I38" s="547"/>
+      <c r="J38" s="655"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="30.00" customWidth="1"/>
+    <col min="2" max="2" width="30.00" customWidth="1"/>
+    <col min="3" max="3" width="11.00" customWidth="1"/>
+    <col min="4" max="4" width="11.00" customWidth="1"/>
+    <col min="5" max="5" width="15.00" customWidth="1"/>
+    <col min="6" max="6" width="42.00" customWidth="1"/>
+    <col min="7" max="7" width="42.00" customWidth="1"/>
+    <col min="8" max="8" width="38.00" customWidth="1"/>
+    <col min="9" max="9" width="62.00" customWidth="1"/>
+    <col min="10" max="10" width="90.00" customWidth="1"/>
+    <col min="11" max="11" width="11.00" customWidth="1"/>
+    <col min="12" max="12" width="55.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Rights Holder</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="C1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Term</t>
+        </is>
+      </c>
+      <c r="D1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E1" s="602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Impact (USD m)</t>
+        </is>
+      </c>
+      <c r="F1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior Revenue in Region</t>
+        </is>
+      </c>
+      <c r="G1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New / Current Revenue in Region</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What's Changing</t>
+        </is>
+      </c>
+      <c r="I1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Notes</t>
+        </is>
+      </c>
+      <c r="K1" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="E2" s="546">
+        <v>50</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney US: ~$87.5m a year on the 2023-25 cycle (Sports Business Journal, Jun 2023)</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple: ~$140m average over the five-year term, ~$131-132m in 2026 (SBJ, Oct 2025: ~56% above ESPN)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replacing ESPN / Disney at roughly 50% more money</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">US rights move from ESPN (~$87.5m/yr) to Apple (~$140m/yr), a ~60% uplift and the largest single swing in the book.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apple pays about $140m a year against the ~$87.5m ESPN paid - a ~60% uplift on the region. The workbook carries $131.5m for 2026 because it starts below the term average and steps to $145m by 2028, so the modelled delta is ~+$44m; the trade-reported delta is ~+$50m. We use the trade numbers. Largest single swing in the book and the whole of the US change: ESPN's $87.5m also drops out of 2025, and the two must be read as one line.</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/
+https://www.sportsbusinessjournal.com/Articles/2025/10/17/f1-apple-clinch-five-year-media-rights-deal-as-racing-series-pins-us-hopes-on-tech-giant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPN / Disney</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America &amp; Caribbean (ex-Brazil, ex-Mexico)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E3" s="546">
+        <v>1.3</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior LatAm/Caribbean cycle, not disclosed. Back-solved at ~$33.7m from the 2026 level (the 2015-19 Mediapro cycle ran at EUR20m+)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current estimate: ~$35.0m for 2026 (EST - no fee published)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewing at ~4%, not landing $35m of new money</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-28 extension signed Feb 2026 with no fee; booked as a ~4% escalator on a ~$33.7m base.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026-28 extension was announced in Feb 2026 with no fee. The model books nothing in 2025, which makes the sheet look like a +$35m new deal; in reality these rights existed all along, so the change is an escalation on a ~$33.7m base. If the new cycle were flat, the delta is zero. Modelled, not reported.</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="E4" s="546">
+        <v>-7</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Band: ~$15m a year on the 2023-25 cycle (Folha de S.Paulo)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globo: ~$8m a year, ~$7.7m in the 2026 model year (UOL)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replacing Band at roughly half the fee</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazilian rights move from Band (~$15m) to Globo (~$8m), a ~-$7m step, the only large market going backwards.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The one large market where the renewal went backwards. Globo traded fee for reach - 15 races free-to-air plus every session on sportv - and Record reportedly bid ~$13m and lost. Net change is about -$7m, not the +$8m a naive new-deal reading gives.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-returns-to-globo-in-multi-year-broadcast-deal-from-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2037</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E5" s="546">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior UK/Ireland cycle, ~$84m a year</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New five-year extension (May 2026) reportedly worth ~$1bn in total, or ~$125m a year; ~$93m in 2026 on the model's path</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New contract at a materially higher price</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Five-year extension to 2034 announced May 2026, reported at ~GBP1bn (~$125m/yr) versus ~$84m previously.</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky extended UK/Ireland by five years to 2034 (announced 6 May 2026); the press report the extension as a ~GBP1bn deal. Our model carries one blended UK/Ireland/Italy row at $117m for 2025 stepping 3% a year, which cannot show a contract step. The ~$10m here is directional: the workbook number does not move, only the attribution does. No fee was disclosed by either party.</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-and-sky-agree-long-term-partnership-across-uk-ireland-and-italy/
+https://www.skysports.com/f1/news/13540672/sky-sports-to-remain-home-of-formula-1-until-2034-after-five-year-extension-to-exclusive-uk-and-ireland-deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2032</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E6" s="546">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior Italian cycle, fee undisclosed</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extended five years to 2032 alongside UK/Ireland; no value published</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No visible change</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy extended to 2032 in the same May 2026 announcement; no fee published.</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy was extended in the same May 2026 announcement. Neither party published a fee, so nothing can be estimated beyond no step reported. Shown so the UK row above is not read as covering Italy too.</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No data</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/formula-1-and-sky-agree-long-term-partnership-across-uk-ireland-and-italy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Deutschland (RTL Group)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2027</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E7" s="546">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current cycle, ~EUR50-55m a year (Sport Bild, GPBlog, WEB.DE)</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No new contract yet - the 2028 tender is live</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing yet, but the biggest known upside</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rights run to 2027; the 2028 tender is live and unbooked, with Apple and Amazon named as interested.</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RTL now owns Sky Deutschland, F1 has confirmed a competitive tender and Apple and Amazon have both been named as interested. A renewed German deal at pass-through value is the most likely step change after the US. Nothing is booked because no contract exists.</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No data</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canal+</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France, Monaco &amp; Francophone Africa</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-2029</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E8" s="546">
+        <v>3.3</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior French cycle, ~$65m a year (L'Equipe: &gt;EUR60m)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current: ~$81.9m for 2025 per the model, escalated ~4%</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal with a significant increase, already inside the base</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract runs to 2029 with a ~4% escalator; no repricing event in 2026.</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L'Equipe reported the deal at more than EUR60m a year and Canal+ management called the renewal a significant increase, so part of the 2026 level is already a step rather than an escalator. Francophone Africa is bundled in the fee. Treat the $3.3m as an escalator; the step is upstream of 2025 and does not appear in this period.</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain, Andorra &amp; Portugal</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2030</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E9" s="546">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telefonica Spain, ~EUR45m a year</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN Iberia, estimated ~$62m for 2025 (Spanish press: EUR40-50m for Spain plus Portugal)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already stepped up when DAZN took Iberia in 2024</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iberia rights moved to DAZN in 2024 at ~$62m; 2026 carries only escalation.</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Telefonica-to-DAZN move is the step, and it landed before 2025, so 2026 is pure escalation. DAZN took exclusivity and added Portugal, which is why the model sits above the EUR45m Telefonica face value. A buy-side note puts Spain, Germany and Italy combined at ~$250m against ~$183m booked - the rows were not re-based to close that gap.</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands &amp; Nordics</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2029</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E10" s="546">
+        <v>17</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior Netherlands-only cycle, ~$30m a year</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay, ~$47m a year (Sportcal), ~$45-47m for 2025-26 in the model</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New 2025-29 contract doubles the Dutch fee and adds the Nordics</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-29 contract lifted the Dutch fee from ~$30m to ~$47m and added the Nordics.</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dutch press put the Netherlands alone at ~EUR45m, up from ~$30m in the prior cycle, and the 2025-29 package now bundles the Nordics. The step landed in 2025, so 2026 only carries the escalator; listed here because it is one of the steeper renewals in the book and explains why the row sits so high.</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle East, North Africa &amp; Turkiye</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-2033</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E11" s="546">
+        <v>1.7</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-2024 MENA cycle, fee undisclosed</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN, &gt;$500m over ten years, ~$50m a year term average (Bloomberg, Reuters)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small 2026 rail; the step landed in 2024</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ten-year deal from 2024 at ~$50m/yr average; 2026 carries only escalation.</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A 2024 renewal, so 2026 carries only escalation plus the fact that early years of a stepped contract sit below the term average. No repricing event in this window.</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports / Polsat</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poland</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E12" s="546">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viaplay, ~$15m a year (GlobalData / Sportcal)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports, ~$16.0m in the model; Polsat called the fee a record</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New 2025-28 contract at a record Polish fee</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports replaced Viaplay in 2025 at a record Polish fee, modelled ~$1-2m above the prior cycle.</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eleven Sports displaced Viaplay from 2025 at a fee Polsat described as a record without publishing it. The model puts it ~$1-2m above the prior cycle. Direction of travel is reliable; magnitude is not. The step landed in 2025.</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://grupapolsatplus.pl/en/archive/formula-1-back-eleven-sports-network-has-secured-exclusive-rights-next-four-seasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTVA / M4 Sport (via Hungaroring Sport)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-2027</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E13" s="546">
+        <v>0.6</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior package, $43.4m over 2023-25 (~$14.5m a year, Magyar Hang)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-27 renewal agreed Dec 2025, fee undisclosed</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewed on broadly the same terms</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewed Dec 2025 through 2027 at an undisclosed fee; booked as a ~4% escalator on ~$14.5m.</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The December 2025 renewal carries no published fee and the model escalates the prior $14.5m a year, so the small uplift is escalator, not step. If the renewal was flat the delta is zero.</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sports Mexico / Televisa</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-2028</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E14" s="546">
+        <v>1.8</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports, ~$1.5m for the last six races of 2025 (~$6m annualised, distressed exit)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Televisa/Sky, ~$7.8m in 2026 (EST - no fee published)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Televisa repriced upward late in 2025</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Televisa/Sky replaced Fox Sports at ~$7.8m versus a distressed ~$6m run rate.</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports exited Mexico at a distressed ~$6m annualised run rate; Televisa renewed above it. The ~$1.8m is mostly escalation, with a modest step on top. Nothing is booked in 2025 because Fox held the tail, which flatters the year-on-year look.</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E15" s="546">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAZN-era Japan, roughly $12-15m a year (not published)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV exclusive, ~$19.6-20.3m in 2026 (Sponichi: several billion yen)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New exclusive five-year deal replacing a split package</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV took exclusive Japanese rights from 2026 at ~$20.3m, replacing a split DAZN-led package worth ~$12-15m.</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuji TV took exclusive Japanese rights from 2026 across free-to-air, FOD and F1 TV distribution, replacing DAZN. F1 disclosed the term, not the fee; Sponichi's several-billion-yen report is a very wide bracket. The model books $20.3m. The step rather than the $20.3m is the number that matters - if prior Japan was ~$12m the step is ~$8m, if it was ~$18m it is ~$2m. Modelled.</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/fuji-tv-to-exclusively-broadcast-formula-1-in-japan-in-new-long-term-deal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN Sports</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia (10 territories)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2030</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E16" s="546">
+        <v>0.9</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior cycle, ~$22m a year (EST)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beIN, ~$23m in 2026 (EST - no fee published)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal at the book rate</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-Asia extension signed Feb 2026 with no fee; booked as a ~4% escalator on ~$22m.</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pan-Asia extension was announced in Feb 2026 with no fee. Booked as a 4% escalation on the prior level; there is no evidence of a step in either direction.</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupang Play, ELTA, Videoland</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korea, Chinese Taipei &amp; residual SE Asia</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2029</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E17" s="546">
+        <v>0.2</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior cycle, ~$4.3m a year (EST)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-contracted, ~$4.5m in 2026 (EST - nothing published)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal at the book rate</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small basket re-contracted in 2026 at ~$4.5m; no fee published for any deal.</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No value published for any deal in this basket. Least-supported row in the book and the first candidate for revision if a single fee surfaces.</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky Sport New Zealand</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Zealand</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-up</t>
+        </is>
+      </c>
+      <c r="E18" s="546">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior cycle, ~$1.5m a year (Coliseum)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky NZ, ~$2.8-3.0m in 2026 (no fee published)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doubling on the Lawson-era interest uplift</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three-year renewal from 2026 modelled at ~$2.9m, roughly double the prior ~$1.5m.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky renewed for three years in Sep 2025. Prior history is ~$1.5m a year; the model doubles it on the back of the surge in New Zealand interest. That doubling is our assumption, not a reported step. Small in dollars, high in relative uncertainty.</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV360 (Viettel)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vietnam</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-2028</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New deal</t>
+        </is>
+      </c>
+      <c r="E19" s="546">
+        <v>1.9</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No predecessor - Vietnam had no F1 broadcaster</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV360, ~$1.9m in 2026 (EST - no fee published)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New market entry</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vietnam had no F1 broadcaster; TV360 took exclusive rights from 2026 at a modelled ~$1.9m.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viettel's TV360 took exclusive Vietnamese rights from 2026. No prior broadcaster and no published fee, so the whole $1.9m is a modelled floor for a single-country streaming deal.</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fox Sports / Foxtel / Kayo</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-2032</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal</t>
+        </is>
+      </c>
+      <c r="E20" s="546">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incumbent contract, ~A$45m a year</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same contract in 2026 at the 4% escalator</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No change in 2026 - the step lands in 2027</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026 is an ordinary escalator year; the A$60m contract step lands in 2027.</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed here only to make the point explicit: 2026 is an ordinary escalation year in Australia. The new A$60m contract starts in 2027 and is on the 2026-2027 summary.</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://corp.formula1.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula 1 (DTC) - F1 TV</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global ex-US</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2018-open</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural</t>
+        </is>
+      </c>
+      <c r="E21" s="546">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FY2025 subscription revenue $181.8m (Liberty Media 10-K)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Held flat in 2026 by the model</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">US subscribers roll into Apple</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FY2025 subscription revenue was $181.8m (10-K); held flat in 2026 as US subscribers move to Apple.</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported, audited and flat. The US portion of F1 TV subscriptions transfers to Apple in 2026, so the line is held flat and the growth is treated as upside. No step-up to book, but it is the one line that is a filed number rather than an estimate.</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/1560385/000110465926020653/lmca-20251231x10k.htm
+https://www.apple.com/newsroom/2025/10/apple-is-the-exclusive-new-broadcast-partner-for-formula-1-in-the-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NET CHANGE — rows above</t>
+        </is>
+      </c>
+      <c r="B22" s="7">
+        <v>94.4</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="547"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="3"/>
     </row>
   </sheetData>
 </worksheet>
